--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>517.468</t>
+          <t>253.617</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>154.22</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>157.66</t>
+          <t>157.78</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>156.07</t>
+          <t>155.95</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.94</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>77078460.4</t>
+          <t>75418593.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>83740554.0</t>
+          <t>69462697.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>148438894.86</t>
+          <t>147915441.16</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6662093</t>
+          <t>5955895</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-13224559.91433039</t>
+          <t>-13177221.73576224</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-10700633.4</v>
+        <v>-12916861.75</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,37 +1182,37 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>634.036</t>
+          <t>517.468</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-24.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>154.88</t>
+          <t>154.22</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>157.54</t>
+          <t>157.66</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>156.07</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.14</t>
+          <t>-121.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>73964298.0</t>
+          <t>77078460.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>97688090.1</t>
+          <t>83740554.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>148383127.96</t>
+          <t>148438894.86</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-23723792</t>
+          <t>-6662093</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-13683455.64394853</t>
+          <t>-13224559.91433039</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-11420753.81</v>
+        <v>-10700633.4</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,37 +1613,37 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>148.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>149.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>656.712</t>
+          <t>634.036</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.97</t>
+          <t>-24.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>154.6</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>154.88</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>157.43</t>
+          <t>157.54</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>156.51</t>
+          <t>156.28</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-24.10</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.63</t>
+          <t>-120.14</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>100112352.0</t>
+          <t>95173237.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>65836229.8</t>
+          <t>73964298.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>98222294.2</t>
+          <t>97688090.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>147860696.88</t>
+          <t>148383127.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-32386064</t>
+          <t>-23723792</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-14094855.97693689</t>
+          <t>-13683455.64394853</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-13899869.76</v>
+        <v>-11420753.81</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,22 +2044,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>426.802</t>
+          <t>656.712</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-38.64</t>
+          <t>-32.97</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>155.4</t>
+          <t>154.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>156.48</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>157.34</t>
+          <t>157.43</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>156.75</t>
+          <t>156.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>-24.10</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.51</t>
+          <t>-118.63</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>65986071.0</t>
+          <t>100112352.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>57569022.4</t>
+          <t>65836229.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>93825463.8</t>
+          <t>98222294.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>146775704.64</t>
+          <t>147860696.88</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-36256441</t>
+          <t>-32386064</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-14130308.01572335</t>
+          <t>-14094855.97693689</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-17474230.95</v>
+        <v>-13899869.76</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,37 +2475,37 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>300.495</t>
+          <t>426.802</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-38.64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>155.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>157.32</t>
+          <t>156.48</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>157.34</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>156.88</t>
+          <t>156.75</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-13.95</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-117.51</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>46291133.0</t>
+          <t>65986071.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>63506802.6</t>
+          <t>57569022.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>95637445.0</t>
+          <t>93825463.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>146570119.66</t>
+          <t>146775704.64</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-32130642</t>
+          <t>-36256441</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-13522322.02727396</t>
+          <t>-14130308.01572335</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-18299994.29</v>
+        <v>-17474230.95</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>398.559</t>
+          <t>300.495</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>156.2</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>158.55</t>
+          <t>157.32</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>157.02</t>
+          <t>156.88</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-15.91</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>62258697.0</t>
+          <t>46291133.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>90402647.6</t>
+          <t>63506802.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>101054998.5</t>
+          <t>95637445.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>147052834.54</t>
+          <t>146570119.66</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-10652350</t>
+          <t>-32130642</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12653654.34228084</t>
+          <t>-13522322.02727396</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-16715913.06</v>
+        <v>-18299994.29</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>349.772</t>
+          <t>398.559</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3600,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>59.65</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>156.9</t>
+          <t>156.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>159.88</t>
+          <t>158.55</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>156.96</t>
+          <t>157.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>157.15</t>
+          <t>157.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-28.64</t>
+          <t>-15.91</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-115.64</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>54532896.0</t>
+          <t>62258697.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>121411882.2</t>
+          <t>90402647.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>99798952.2</t>
+          <t>101054998.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>146779920.26</t>
+          <t>147052834.54</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>21612930</t>
+          <t>-10652350</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-11915061.8482831</t>
+          <t>-12653654.34228084</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-15566753.4</v>
+        <v>-16715913.06</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,37 +3768,37 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>158.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>382.118</t>
+          <t>349.772</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.81</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>156.3</t>
+          <t>156.9</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>161.15</t>
+          <t>159.88</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>156.71</t>
+          <t>156.96</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>157.38</t>
+          <t>157.15</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-54.84</t>
+          <t>-28.64</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-115.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>58776315.0</t>
+          <t>54532896.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>130608358.6</t>
+          <t>121411882.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>100613378.5</t>
+          <t>99798952.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>146823636.06</t>
+          <t>146779920.26</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>29994980</t>
+          <t>21612930</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-11251117.92990897</t>
+          <t>-11915061.8482831</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-12541376.87</v>
+        <v>-15566753.4</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,17 +4199,17 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>617.031</t>
+          <t>382.118</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>156.3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>162.38</t>
+          <t>161.15</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>156.71</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>157.62</t>
+          <t>157.38</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-75.23</t>
+          <t>-54.84</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.53</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>95674972.0</t>
+          <t>58776315.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>130081905.2</t>
+          <t>130608358.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>114075850.4</t>
+          <t>100613378.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>146732628.72</t>
+          <t>146823636.06</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>16006054</t>
+          <t>29994980</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-11016525.395184</t>
+          <t>-11251117.92990897</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-8226156.12</v>
+        <v>-12541376.87</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,17 +4710,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1147.22</t>
+          <t>617.031</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>163.8</t>
+          <t>162.38</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>156.43</t>
+          <t>156.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>157.93</t>
+          <t>157.62</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-106.05</t>
+          <t>-75.23</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.17</t>
+          <t>-112.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>180770358.0</t>
+          <t>95674972.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>127768087.4</t>
+          <t>130081905.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>110349065.4</t>
+          <t>114075850.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>145979443.4</t>
+          <t>146732628.72</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17419022</t>
+          <t>16006054</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11523865.26329266</t>
+          <t>-11016525.395184</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-5721191.29</v>
+        <v>-8226156.12</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1361.212</t>
+          <t>1147.22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-6.69</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>164.72</t>
+          <t>163.8</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>156.24</t>
+          <t>156.43</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>158.11</t>
+          <t>157.93</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-209.56</t>
+          <t>-106.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.47</t>
+          <t>-110.17</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>193147945.825615</t>
+          <t>192951182.4559249</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>217304870.0</t>
+          <t>180770358.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>111707349.4</t>
+          <t>127768087.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>112057916.2</t>
+          <t>110349065.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>143259927.56</t>
+          <t>145979443.4</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-350566</t>
+          <t>17419022</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-12578896.89399887</t>
+          <t>-11523865.26329266</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-11055704.64</v>
+        <v>-5721191.29</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-10.48</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>17.32242936015869</t>
+          <t>2.441263654364586</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-3.235065544713983</t>
+          <t>7.034222544205167</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>17.52616495665033</t>
+          <t>13.92772423591407</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>161.5</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>446.427</t>
+          <t>639.921</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,122 +5770,122 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>22.14</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>31.31</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-91.86</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>17988708.97543353</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>14958432.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>11577776.6</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>9216007.8</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>9691364.4</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>2361768</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-36417.19768447067</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>481359.49</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-92.50</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>17982270.56874096</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>10462814.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>10425234.4</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>9338847.5</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>9424082.38</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>1086386</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-130558.4136477165</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>132817.27</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
       <c r="BF13" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -5923,27 +5923,27 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>-11.96949300641144</t>
+          <t>11.95148944019183</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-28.65893001245509</t>
+          <t>-23.56482151964889</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-6.154330396374816</t>
+          <t>-10.04313818682466</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6050,104 +6050,104 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>446.427</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>561.564</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>11.63</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>23.25</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>0</t>
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-92.99</t>
+          <t>-92.50</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17982270.56874096</t>
+          <t>17988708.97543353</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>9893437.4</t>
+          <t>10425234.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9338756.6</t>
+          <t>9338847.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>9295806.7</t>
+          <t>9424082.38</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>554680</t>
+          <t>1086386</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-178444.901985053</t>
+          <t>-130558.4136477165</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>111829.7</v>
+        <v>132817.27</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,22 +6354,22 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>-11.96949300641144</t>
+          <t>11.95148944019183</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-28.65893001245509</t>
+          <t>-23.56482151964889</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-6.154330396374816</t>
+          <t>-10.04313818682466</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>576.54</t>
+          <t>561.564</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,33 +6591,33 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,57 +6627,57 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>83.26</t>
+          <t>96.08</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-93.18</t>
+          <t>-92.99</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17982270.56874096</t>
+          <t>17988708.97543353</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>13413808.0</t>
+          <t>13036399.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>8387023.4</t>
+          <t>9893437.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8939602.7</t>
+          <t>9338756.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>9062267.64</t>
+          <t>9295806.7</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-552579</t>
+          <t>554680</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-231222.1025627005</t>
+          <t>-178444.901985053</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-197887.71</v>
+        <v>111829.7</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6785,22 +6785,22 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>-11.96949300641144</t>
+          <t>11.95148944019183</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-28.65893001245509</t>
+          <t>-23.56482151964889</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-6.154330396374816</t>
+          <t>-10.04313818682466</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>264.169</t>
+          <t>576.54</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-20.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,72 +7043,72 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>83.26</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-56.73</t>
+          <t>-15.88</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-92.91</t>
+          <t>-93.18</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17982270.56874096</t>
+          <t>17988708.97543353</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>6017430.0</t>
+          <t>13413808.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>7083012.6</t>
+          <t>8387023.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>8900627.2</t>
+          <t>8939602.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>8842829.82</t>
+          <t>9062267.64</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1817614</t>
+          <t>-552579</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-237282.9010257832</t>
+          <t>-231222.1025627005</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-673710.42</v>
+        <v>-197887.71</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,32 +7216,32 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>-11.96949300641144</t>
+          <t>11.95148944019183</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-28.65893001245509</t>
+          <t>-23.56482151964889</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-6.154330396374816</t>
+          <t>-10.04313818682466</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>403.272</t>
+          <t>264.169</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-20.42</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,67 +7474,67 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-63.95</t>
+          <t>-56.73</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-92.91</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17982270.56874096</t>
+          <t>17988708.97543353</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>9195721.0</t>
+          <t>6017430.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>6854239.0</t>
+          <t>7083012.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>8862595.7</t>
+          <t>8900627.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>8796355.32</t>
+          <t>8842829.82</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2008356</t>
+          <t>-1817614</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-157932.4435127094</t>
+          <t>-237282.9010257832</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-536926.98</v>
+        <v>-673710.42</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,32 +7647,32 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>-11.96949300641144</t>
+          <t>11.95148944019183</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-28.65893001245509</t>
+          <t>-23.56482151964889</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-6.154330396374816</t>
+          <t>-10.04313818682466</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>348.023</t>
+          <t>403.272</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,275 +7905,275 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
+          <t>22.92</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>22.23</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>22.01</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-63.95</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-91.90</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>17988708.97543353</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>9195721.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>6854239.0</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>8862595.7</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>8796355.32</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-2008356</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-157932.4435127094</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>-536926.98</v>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>56.07</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>43.72%</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>4219</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>岱宇-運動休閒-上市</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>22.9</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>-74.11</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-90.60</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>17982270.56874096</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>7803829.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>8252460.6</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>8745649.0</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>8646425.52</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>-493188</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>-89024.34543927149</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>-662877.29</v>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>-11.96949300641144</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>-28.65893001245509</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>-6.154330396374816</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="BT18" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="BU18" t="inlineStr">
-        <is>
-          <t>56.07</t>
-        </is>
-      </c>
-      <c r="BV18" t="inlineStr">
-        <is>
-          <t>43.72%</t>
-        </is>
-      </c>
-      <c r="BW18" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="BX18" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
-      <c r="BY18" t="inlineStr">
-        <is>
-          <t>4219</t>
-        </is>
-      </c>
-      <c r="BZ18" t="inlineStr">
-        <is>
-          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA18" t="inlineStr">
-        <is>
-          <t>岱宇-運動休閒-上市</t>
-        </is>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="CC18" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>22.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>245.739</t>
+          <t>348.023</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,37 +8336,37 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -8386,27 +8386,27 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-70.36</t>
+          <t>-74.11</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.86</t>
+          <t>-90.60</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>17982270.56874096</t>
+          <t>17988708.97543353</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>5504329.0</t>
+          <t>7803829.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>8784075.8</t>
+          <t>8252460.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8506553.8</t>
+          <t>8745649.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>8565549.34</t>
+          <t>8646425.52</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>277522</t>
+          <t>-493188</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>15312.55384128857</t>
+          <t>-89024.34543927149</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-670000.83</v>
+        <v>-662877.29</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,27 +8509,27 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>-11.96949300641144</t>
+          <t>11.95148944019183</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-28.65893001245509</t>
+          <t>-23.56482151964889</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-6.154330396374816</t>
+          <t>-10.04313818682466</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>311.454</t>
+          <t>245.739</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.98</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-62.83</t>
+          <t>-70.36</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-86.90</t>
+          <t>-88.86</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17982270.56874096</t>
+          <t>17988708.97543353</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6893754.0</t>
+          <t>5504329.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>9492182.0</t>
+          <t>8784075.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>9593018.2</t>
+          <t>8506553.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>8490905.06</t>
+          <t>8565549.34</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-100836</t>
+          <t>277522</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>139914.9870893983</t>
+          <t>15312.55384128857</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-409873.71</v>
+        <v>-670000.83</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,32 +8940,32 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>-11.96949300641144</t>
+          <t>11.95148944019183</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-28.65893001245509</t>
+          <t>-23.56482151964889</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-6.154330396374816</t>
+          <t>-10.04313818682466</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>217.146</t>
+          <t>311.454</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,32 +9218,32 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -9253,22 +9253,22 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-41.72</t>
+          <t>-62.83</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-86.90</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17982270.56874096</t>
+          <t>17988708.97543353</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>4873562.0</t>
+          <t>6893754.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>10718241.8</t>
+          <t>9492182.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>12106318.1</t>
+          <t>9593018.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>8416563.16</t>
+          <t>8490905.06</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1388076</t>
+          <t>-100836</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>239876.5684125876</t>
+          <t>139914.9870893983</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-172492.16</v>
+        <v>-409873.71</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-11.96949300641144</t>
+          <t>11.95148944019183</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-28.65893001245509</t>
+          <t>-23.56482151964889</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-6.154330396374816</t>
+          <t>-10.04313818682466</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>724.961</t>
+          <t>217.146</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-16.09</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,52 +9629,52 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -9684,22 +9684,22 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-32.95</t>
+          <t>-41.72</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-83.27</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17982270.56874096</t>
+          <t>17988708.97543353</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>16186829.0</t>
+          <t>4873562.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>10870952.4</t>
+          <t>10718241.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>12955506.5</t>
+          <t>12106318.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>8421075.14</t>
+          <t>8416563.16</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2084554</t>
+          <t>-1388076</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>314852.7004724934</t>
+          <t>239876.5684125876</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>389233.92</v>
+        <v>-172492.16</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9802,22 +9802,22 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-11.96949300641144</t>
+          <t>11.95148944019183</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-28.65893001245509</t>
+          <t>-23.56482151964889</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-6.154330396374816</t>
+          <t>-10.04313818682466</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>460.783</t>
+          <t>724.961</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-24.26</t>
+          <t>-16.09</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>640</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,37 +10075,37 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-32.95</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-81.89</t>
+          <t>-83.27</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17982270.56874096</t>
+          <t>17988708.97543353</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>10461905.0</t>
+          <t>16186829.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>9238837.4</t>
+          <t>10870952.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>12198900.1</t>
+          <t>12955506.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>8169948.84</t>
+          <t>8421075.14</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2960062</t>
+          <t>-2084554</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>301328.841940909</t>
+          <t>314852.7004724934</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-34337.21</v>
+        <v>389233.92</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-11.96949300641144</t>
+          <t>11.95148944019183</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-28.65893001245509</t>
+          <t>-23.56482151964889</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-6.154330396374816</t>
+          <t>-10.04313818682466</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>253.617</t>
+          <t>523.223</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.37</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>153.07</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>157.78</t>
+          <t>157.86</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>155.74</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-32.26</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-125.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>75418593.0</t>
+          <t>77542911.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>69462697.8</t>
+          <t>67555966.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>147915441.16</t>
+          <t>148067039.32</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5955895</t>
+          <t>9986944</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-13177221.73576224</t>
+          <t>-12880589.18892824</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-12916861.75</v>
+        <v>-11249110.18</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>517.468</t>
+          <t>253.617</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>154.22</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>157.66</t>
+          <t>157.78</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>156.07</t>
+          <t>155.95</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.94</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>77078460.4</t>
+          <t>75418593.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>83740554.0</t>
+          <t>69462697.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>148438894.86</t>
+          <t>147915441.16</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6662093</t>
+          <t>5955895</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-13224559.91433039</t>
+          <t>-13177221.73576224</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-10700633.4</v>
+        <v>-12916861.75</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1698,17 +1698,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>634.036</t>
+          <t>517.468</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-24.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>154.88</t>
+          <t>154.22</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>157.54</t>
+          <t>157.66</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>156.07</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.14</t>
+          <t>-121.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>73964298.0</t>
+          <t>77078460.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>97688090.1</t>
+          <t>83740554.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>148383127.96</t>
+          <t>148438894.86</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-23723792</t>
+          <t>-6662093</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-13683455.64394853</t>
+          <t>-13224559.91433039</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-11420753.81</v>
+        <v>-10700633.4</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>148.5</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>149.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>656.712</t>
+          <t>634.036</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.97</t>
+          <t>-24.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>154.6</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>154.88</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>157.43</t>
+          <t>157.54</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>156.51</t>
+          <t>156.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-24.10</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.63</t>
+          <t>-120.14</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>100112352.0</t>
+          <t>95173237.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>65836229.8</t>
+          <t>73964298.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>98222294.2</t>
+          <t>97688090.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>147860696.88</t>
+          <t>148383127.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-32386064</t>
+          <t>-23723792</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-14094855.97693689</t>
+          <t>-13683455.64394853</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-13899869.76</v>
+        <v>-11420753.81</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>426.802</t>
+          <t>656.712</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-38.64</t>
+          <t>-32.97</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>155.4</t>
+          <t>154.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>156.48</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>157.34</t>
+          <t>157.43</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>156.75</t>
+          <t>156.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>-24.10</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.51</t>
+          <t>-118.63</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>65986071.0</t>
+          <t>100112352.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>57569022.4</t>
+          <t>65836229.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>93825463.8</t>
+          <t>98222294.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>146775704.64</t>
+          <t>147860696.88</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-36256441</t>
+          <t>-32386064</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-14130308.01572335</t>
+          <t>-14094855.97693689</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-17474230.95</v>
+        <v>-13899869.76</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>300.495</t>
+          <t>426.802</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-38.64</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>155.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>157.32</t>
+          <t>156.48</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>157.34</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>156.88</t>
+          <t>156.75</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-13.95</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-117.51</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>46291133.0</t>
+          <t>65986071.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>63506802.6</t>
+          <t>57569022.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>95637445.0</t>
+          <t>93825463.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>146570119.66</t>
+          <t>146775704.64</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-32130642</t>
+          <t>-36256441</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-13522322.02727396</t>
+          <t>-14130308.01572335</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-18299994.29</v>
+        <v>-17474230.95</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>398.559</t>
+          <t>300.495</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>156.2</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>158.55</t>
+          <t>157.32</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>157.02</t>
+          <t>156.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-15.91</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>62258697.0</t>
+          <t>46291133.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>90402647.6</t>
+          <t>63506802.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>101054998.5</t>
+          <t>95637445.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>147052834.54</t>
+          <t>146570119.66</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-10652350</t>
+          <t>-32130642</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12653654.34228084</t>
+          <t>-13522322.02727396</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-16715913.06</v>
+        <v>-18299994.29</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>349.772</t>
+          <t>398.559</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>59.65</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>156.9</t>
+          <t>156.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>159.88</t>
+          <t>158.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>156.96</t>
+          <t>157.14</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>157.15</t>
+          <t>157.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-28.64</t>
+          <t>-15.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-115.64</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>54532896.0</t>
+          <t>62258697.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>121411882.2</t>
+          <t>90402647.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>99798952.2</t>
+          <t>101054998.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>146779920.26</t>
+          <t>147052834.54</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>21612930</t>
+          <t>-10652350</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-11915061.8482831</t>
+          <t>-12653654.34228084</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-15566753.4</v>
+        <v>-16715913.06</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>158.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>382.118</t>
+          <t>349.772</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.81</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>156.3</t>
+          <t>156.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>161.15</t>
+          <t>159.88</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>156.71</t>
+          <t>156.96</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>157.38</t>
+          <t>157.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-54.84</t>
+          <t>-28.64</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-115.64</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>58776315.0</t>
+          <t>54532896.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>130608358.6</t>
+          <t>121411882.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>100613378.5</t>
+          <t>99798952.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>146823636.06</t>
+          <t>146779920.26</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>29994980</t>
+          <t>21612930</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-11251117.92990897</t>
+          <t>-11915061.8482831</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-12541376.87</v>
+        <v>-15566753.4</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>617.031</t>
+          <t>382.118</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>156.3</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>162.38</t>
+          <t>161.15</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>156.71</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>157.62</t>
+          <t>157.38</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-75.23</t>
+          <t>-54.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.53</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>95674972.0</t>
+          <t>58776315.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>130081905.2</t>
+          <t>130608358.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>114075850.4</t>
+          <t>100613378.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>146732628.72</t>
+          <t>146823636.06</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>16006054</t>
+          <t>29994980</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11016525.395184</t>
+          <t>-11251117.92990897</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-8226156.12</v>
+        <v>-12541376.87</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1147.22</t>
+          <t>617.031</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5319,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>523</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>163.8</t>
+          <t>162.38</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>156.43</t>
+          <t>156.57</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>157.93</t>
+          <t>157.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-106.05</t>
+          <t>-75.23</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.17</t>
+          <t>-112.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>192951182.4559249</t>
+          <t>192838571.0692641</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>180770358.0</t>
+          <t>95674972.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>127768087.4</t>
+          <t>130081905.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>110349065.4</t>
+          <t>114075850.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>145979443.4</t>
+          <t>146732628.72</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17419022</t>
+          <t>16006054</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11523865.26329266</t>
+          <t>-11016525.395184</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-5721191.29</v>
+        <v>-8226156.12</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-10.48</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,42 +5619,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-5.39</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>412.554</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>639.921</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,78 +5729,78 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-92.18</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17988708.97543353</t>
+          <t>17983079.02380952</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>11577776.6</t>
+          <t>12252577.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9216007.8</t>
+          <t>9667795.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>9691364.4</t>
+          <t>9822957.84</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2361768</t>
+          <t>2584782</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-36417.19768447067</t>
+          <t>14690.10663538189</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>481359.49</v>
+        <v>295780.28</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>446.427</t>
+          <t>639.921</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,122 +6201,122 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>22.14</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>31.31</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-91.86</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>17983079.02380952</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>14958432.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>11577776.6</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>9216007.8</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>9691364.4</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>2361768</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-36417.19768447067</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>481359.49</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-92.50</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>17988708.97543353</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>10462814.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>10425234.4</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>9338847.5</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>9424082.38</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>1086386</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-130558.4136477165</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>132817.27</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
       <c r="BF14" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>561.564</t>
+          <t>446.427</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,92 +6496,92 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-5.61</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-2.16</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>11.63</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>23.25</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-92.99</t>
+          <t>-92.50</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17988708.97543353</t>
+          <t>17983079.02380952</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>9893437.4</t>
+          <t>10425234.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9338756.6</t>
+          <t>9338847.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>9295806.7</t>
+          <t>9424082.38</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>554680</t>
+          <t>1086386</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-178444.901985053</t>
+          <t>-130558.4136477165</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>111829.7</v>
+        <v>132817.27</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>576.54</t>
+          <t>561.564</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6937,22 +6937,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,33 +7022,33 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,57 +7058,57 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>83.26</t>
+          <t>96.08</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-93.18</t>
+          <t>-92.99</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17988708.97543353</t>
+          <t>17983079.02380952</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>13413808.0</t>
+          <t>13036399.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>8387023.4</t>
+          <t>9893437.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>8939602.7</t>
+          <t>9338756.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>9062267.64</t>
+          <t>9295806.7</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-552579</t>
+          <t>554680</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-231222.1025627005</t>
+          <t>-178444.901985053</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-197887.71</v>
+        <v>111829.7</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,17 +7296,17 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>264.169</t>
+          <t>576.54</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-20.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,72 +7474,72 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>83.26</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-56.73</t>
+          <t>-15.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-92.91</t>
+          <t>-93.18</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17988708.97543353</t>
+          <t>17983079.02380952</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6017430.0</t>
+          <t>13413808.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>7083012.6</t>
+          <t>8387023.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>8900627.2</t>
+          <t>8939602.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>8842829.82</t>
+          <t>9062267.64</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1817614</t>
+          <t>-552579</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-237282.9010257832</t>
+          <t>-231222.1025627005</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-673710.42</v>
+        <v>-197887.71</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>403.272</t>
+          <t>264.169</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-20.42</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,67 +7905,67 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-63.95</t>
+          <t>-56.73</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-92.91</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17988708.97543353</t>
+          <t>17983079.02380952</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>9195721.0</t>
+          <t>6017430.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>6854239.0</t>
+          <t>7083012.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>8862595.7</t>
+          <t>8900627.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>8796355.32</t>
+          <t>8842829.82</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2008356</t>
+          <t>-1817614</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-157932.4435127094</t>
+          <t>-237282.9010257832</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-536926.98</v>
+        <v>-673710.42</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>348.023</t>
+          <t>403.272</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,275 +8336,275 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
+          <t>22.92</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>22.23</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>22.01</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-63.95</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-91.90</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>17983079.02380952</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>9195721.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>6854239.0</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>8862595.7</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>8796355.32</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-2008356</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-157932.4435127094</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>-536926.98</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>53.1</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>43.72%</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>18.13</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>3995</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>岱宇-運動休閒-上市</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>22.9</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-74.11</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-90.60</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>17988708.97543353</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>7803829.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>8252460.6</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>8745649.0</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>8646425.52</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>-493188</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-89024.34543927149</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>-662877.29</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>56.07</t>
-        </is>
-      </c>
-      <c r="BV19" t="inlineStr">
-        <is>
-          <t>43.72%</t>
-        </is>
-      </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BY19" t="inlineStr">
-        <is>
-          <t>4219</t>
-        </is>
-      </c>
-      <c r="BZ19" t="inlineStr">
-        <is>
-          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>岱宇-運動休閒-上市</t>
-        </is>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>22.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>245.739</t>
+          <t>348.023</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,37 +8767,37 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -8817,27 +8817,27 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-70.36</t>
+          <t>-74.11</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-88.86</t>
+          <t>-90.60</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17988708.97543353</t>
+          <t>17983079.02380952</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>5504329.0</t>
+          <t>7803829.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>8784075.8</t>
+          <t>8252460.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>8506553.8</t>
+          <t>8745649.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>8565549.34</t>
+          <t>8646425.52</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>277522</t>
+          <t>-493188</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>15312.55384128857</t>
+          <t>-89024.34543927149</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-670000.83</v>
+        <v>-662877.29</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,12 +9020,12 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>311.454</t>
+          <t>245.739</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.98</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-62.83</t>
+          <t>-70.36</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-86.90</t>
+          <t>-88.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17988708.97543353</t>
+          <t>17983079.02380952</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>6893754.0</t>
+          <t>5504329.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>9492182.0</t>
+          <t>8784075.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9593018.2</t>
+          <t>8506553.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>8490905.06</t>
+          <t>8565549.34</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-100836</t>
+          <t>277522</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>139914.9870893983</t>
+          <t>15312.55384128857</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-409873.71</v>
+        <v>-670000.83</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,42 +9498,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>-2.25</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>311.454</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>217.146</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>4.03</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,32 +9649,32 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -9684,22 +9684,22 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-41.72</t>
+          <t>-62.83</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-86.90</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17988708.97543353</t>
+          <t>17983079.02380952</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4873562.0</t>
+          <t>6893754.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>10718241.8</t>
+          <t>9492182.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>12106318.1</t>
+          <t>9593018.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>8416563.16</t>
+          <t>8490905.06</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1388076</t>
+          <t>-100836</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>239876.5684125876</t>
+          <t>139914.9870893983</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-172492.16</v>
+        <v>-409873.71</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,42 +9797,42 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>724.961</t>
+          <t>217.146</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-16.09</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,52 +10060,52 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-32.95</t>
+          <t>-41.72</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-83.27</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17988708.97543353</t>
+          <t>17983079.02380952</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16186829.0</t>
+          <t>4873562.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>10870952.4</t>
+          <t>10718241.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>12955506.5</t>
+          <t>12106318.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>8421075.14</t>
+          <t>8416563.16</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2084554</t>
+          <t>-1388076</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>314852.7004724934</t>
+          <t>239876.5684125876</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>389233.92</v>
+        <v>-172492.16</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>523.223</t>
+          <t>342.425</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>153.07</t>
+          <t>152.62</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>157.86</t>
+          <t>157.92</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.74</t>
+          <t>155.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-125.58</t>
+          <t>-127.95</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>77542911.0</t>
+          <t>67444352.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>67555966.7</t>
+          <t>66640291.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>148067039.32</t>
+          <t>147939586.16</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>9986944</t>
+          <t>804061</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12880589.18892824</t>
+          <t>-12718123.77158551</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-11249110.18</v>
+        <v>-11824563.98</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-17.56</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>253.617</t>
+          <t>523.223</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.37</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,17 +1440,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>153.07</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>157.78</t>
+          <t>157.86</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>155.74</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-32.26</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-125.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>75418593.0</t>
+          <t>77542911.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>69462697.8</t>
+          <t>67555966.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>147915441.16</t>
+          <t>148067039.32</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5955895</t>
+          <t>9986944</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-13177221.73576224</t>
+          <t>-12880589.18892824</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-12916861.75</v>
+        <v>-11249110.18</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>517.468</t>
+          <t>253.617</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>154.22</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>157.66</t>
+          <t>157.78</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>156.07</t>
+          <t>155.95</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.94</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>77078460.4</t>
+          <t>75418593.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>83740554.0</t>
+          <t>69462697.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>148438894.86</t>
+          <t>147915441.16</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-6662093</t>
+          <t>5955895</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-13224559.91433039</t>
+          <t>-13177221.73576224</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-10700633.4</v>
+        <v>-12916861.75</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>634.036</t>
+          <t>517.468</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-24.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>154.88</t>
+          <t>154.22</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>157.54</t>
+          <t>157.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>156.07</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.14</t>
+          <t>-121.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>73964298.0</t>
+          <t>77078460.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>97688090.1</t>
+          <t>83740554.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>148383127.96</t>
+          <t>148438894.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-23723792</t>
+          <t>-6662093</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-13683455.64394853</t>
+          <t>-13224559.91433039</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-11420753.81</v>
+        <v>-10700633.4</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>148.5</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>149.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>656.712</t>
+          <t>634.036</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.97</t>
+          <t>-24.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>154.6</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>154.88</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>157.43</t>
+          <t>157.54</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>156.51</t>
+          <t>156.28</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-24.10</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.63</t>
+          <t>-120.14</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>100112352.0</t>
+          <t>95173237.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>65836229.8</t>
+          <t>73964298.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>98222294.2</t>
+          <t>97688090.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>147860696.88</t>
+          <t>148383127.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-32386064</t>
+          <t>-23723792</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-14094855.97693689</t>
+          <t>-13683455.64394853</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-13899869.76</v>
+        <v>-11420753.81</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>426.802</t>
+          <t>656.712</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-38.64</t>
+          <t>-32.97</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>155.4</t>
+          <t>154.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>156.48</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>157.34</t>
+          <t>157.43</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>156.75</t>
+          <t>156.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>-24.10</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.51</t>
+          <t>-118.63</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>65986071.0</t>
+          <t>100112352.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>57569022.4</t>
+          <t>65836229.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>93825463.8</t>
+          <t>98222294.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>146775704.64</t>
+          <t>147860696.88</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-36256441</t>
+          <t>-32386064</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-14130308.01572335</t>
+          <t>-14094855.97693689</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-17474230.95</v>
+        <v>-13899869.76</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>300.495</t>
+          <t>426.802</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-38.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>155.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>157.32</t>
+          <t>156.48</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>157.34</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>156.88</t>
+          <t>156.75</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-13.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-117.51</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>46291133.0</t>
+          <t>65986071.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>63506802.6</t>
+          <t>57569022.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>95637445.0</t>
+          <t>93825463.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>146570119.66</t>
+          <t>146775704.64</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-32130642</t>
+          <t>-36256441</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13522322.02727396</t>
+          <t>-14130308.01572335</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-18299994.29</v>
+        <v>-17474230.95</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>398.559</t>
+          <t>300.495</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>156.2</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>158.55</t>
+          <t>157.32</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>157.02</t>
+          <t>156.88</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-15.91</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>62258697.0</t>
+          <t>46291133.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>90402647.6</t>
+          <t>63506802.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>101054998.5</t>
+          <t>95637445.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>147052834.54</t>
+          <t>146570119.66</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-10652350</t>
+          <t>-32130642</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12653654.34228084</t>
+          <t>-13522322.02727396</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-16715913.06</v>
+        <v>-18299994.29</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>349.772</t>
+          <t>398.559</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-8.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>59.65</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>156.9</t>
+          <t>156.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>159.88</t>
+          <t>158.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>156.96</t>
+          <t>157.14</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>157.15</t>
+          <t>157.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.64</t>
+          <t>-15.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-115.64</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>54532896.0</t>
+          <t>62258697.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>121411882.2</t>
+          <t>90402647.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>99798952.2</t>
+          <t>101054998.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>146779920.26</t>
+          <t>147052834.54</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>21612930</t>
+          <t>-10652350</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-11915061.8482831</t>
+          <t>-12653654.34228084</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-15566753.4</v>
+        <v>-16715913.06</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>158.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>382.118</t>
+          <t>349.772</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29.81</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>156.3</t>
+          <t>156.9</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>161.15</t>
+          <t>159.88</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>156.71</t>
+          <t>156.96</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>157.38</t>
+          <t>157.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-54.84</t>
+          <t>-28.64</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-115.64</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>58776315.0</t>
+          <t>54532896.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>130608358.6</t>
+          <t>121411882.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>100613378.5</t>
+          <t>99798952.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>146823636.06</t>
+          <t>146779920.26</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>29994980</t>
+          <t>21612930</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11251117.92990897</t>
+          <t>-11915061.8482831</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-12541376.87</v>
+        <v>-15566753.4</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>617.031</t>
+          <t>382.118</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>156.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>162.38</t>
+          <t>161.15</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>156.57</t>
+          <t>156.71</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>157.62</t>
+          <t>157.38</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-75.23</t>
+          <t>-54.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.53</t>
+          <t>-114.52</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>192838571.0692641</t>
+          <t>192667952.5785303</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>95674972.0</t>
+          <t>58776315.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>130081905.2</t>
+          <t>130608358.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>114075850.4</t>
+          <t>100613378.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>146732628.72</t>
+          <t>146823636.06</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>16006054</t>
+          <t>29994980</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11016525.395184</t>
+          <t>-11251117.92990897</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-8226156.12</v>
+        <v>-12541376.87</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>412.554</t>
+          <t>130.298</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,72 +5634,72 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-2.16</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,64 +5765,64 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-75.17</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-92.18</t>
+          <t>-93.42</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17983079.02380952</t>
+          <t>17963425.11311239</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>9391435.0</t>
+          <t>2895510.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>12252577.6</t>
+          <t>10148918.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9667795.1</t>
+          <t>9267970.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>9822957.84</t>
+          <t>9823853.94</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2584782</t>
+          <t>880947</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>14690.10663538189</t>
+          <t>-38141.30183444001</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>295780.28</v>
+        <v>-328714.05</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>639.921</t>
+          <t>412.554</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,78 +6160,78 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-92.18</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17983079.02380952</t>
+          <t>17963425.11311239</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>11577776.6</t>
+          <t>12252577.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9216007.8</t>
+          <t>9667795.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>9691364.4</t>
+          <t>9822957.84</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2361768</t>
+          <t>2584782</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-36417.19768447067</t>
+          <t>14690.10663538189</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>481359.49</v>
+        <v>295780.28</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>446.427</t>
+          <t>639.921</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,122 +6632,122 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>22.14</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>31.31</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-91.86</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>17963425.11311239</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>14958432.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>11577776.6</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>9216007.8</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>9691364.4</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>2361768</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-36417.19768447067</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>481359.49</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-92.50</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>17983079.02380952</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>10462814.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>10425234.4</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>9338847.5</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>9424082.38</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>1086386</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-130558.4136477165</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>132817.27</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
       <c r="BF15" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>561.564</t>
+          <t>446.427</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,74 +6927,74 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-7.53</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>11.63</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-5.38</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-2.16</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>23.25</t>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-92.99</t>
+          <t>-92.50</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17983079.02380952</t>
+          <t>17963425.11311239</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>9893437.4</t>
+          <t>10425234.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>9338756.6</t>
+          <t>9338847.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>9295806.7</t>
+          <t>9424082.38</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>554680</t>
+          <t>1086386</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-178444.901985053</t>
+          <t>-130558.4136477165</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>111829.7</v>
+        <v>132817.27</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>576.54</t>
+          <t>561.564</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7368,22 +7368,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,33 +7453,33 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,57 +7489,57 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>83.26</t>
+          <t>96.08</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-93.18</t>
+          <t>-92.99</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17983079.02380952</t>
+          <t>17963425.11311239</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>13413808.0</t>
+          <t>13036399.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>8387023.4</t>
+          <t>9893437.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>8939602.7</t>
+          <t>9338756.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9062267.64</t>
+          <t>9295806.7</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-552579</t>
+          <t>554680</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-231222.1025627005</t>
+          <t>-178444.901985053</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-197887.71</v>
+        <v>111829.7</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>264.169</t>
+          <t>576.54</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-20.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,72 +7905,72 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>83.26</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-56.73</t>
+          <t>-15.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-92.91</t>
+          <t>-93.18</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17983079.02380952</t>
+          <t>17963425.11311239</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>6017430.0</t>
+          <t>13413808.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>7083012.6</t>
+          <t>8387023.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>8900627.2</t>
+          <t>8939602.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>8842829.82</t>
+          <t>9062267.64</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1817614</t>
+          <t>-552579</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-237282.9010257832</t>
+          <t>-231222.1025627005</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-673710.42</v>
+        <v>-197887.71</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>403.272</t>
+          <t>264.169</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-20.42</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,67 +8336,67 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-63.95</t>
+          <t>-56.73</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-92.91</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>17983079.02380952</t>
+          <t>17963425.11311239</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>9195721.0</t>
+          <t>6017430.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>6854239.0</t>
+          <t>7083012.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8862595.7</t>
+          <t>8900627.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>8796355.32</t>
+          <t>8842829.82</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2008356</t>
+          <t>-1817614</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-157932.4435127094</t>
+          <t>-237282.9010257832</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-536926.98</v>
+        <v>-673710.42</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>348.023</t>
+          <t>403.272</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,275 +8767,275 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
+          <t>22.92</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>22.23</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>22.01</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-63.95</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-91.90</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>17963425.11311239</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>9195721.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>6854239.0</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>8862595.7</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>8796355.32</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-2008356</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-157932.4435127094</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>-536926.98</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>52.14</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>43.72%</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>18.27</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>3923</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>岱宇-運動休閒-上市</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>22.9</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-74.11</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-90.60</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>17983079.02380952</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>7803829.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>8252460.6</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>8745649.0</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>8646425.52</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>-493188</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-89024.34543927149</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>-662877.29</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="BT20" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="BV20" t="inlineStr">
-        <is>
-          <t>43.72%</t>
-        </is>
-      </c>
-      <c r="BW20" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>18.13</t>
-        </is>
-      </c>
-      <c r="BY20" t="inlineStr">
-        <is>
-          <t>3995</t>
-        </is>
-      </c>
-      <c r="BZ20" t="inlineStr">
-        <is>
-          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA20" t="inlineStr">
-        <is>
-          <t>岱宇-運動休閒-上市</t>
-        </is>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="CC20" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>22.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>245.739</t>
+          <t>348.023</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,37 +9198,37 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -9248,27 +9248,27 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-70.36</t>
+          <t>-74.11</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-88.86</t>
+          <t>-90.60</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17983079.02380952</t>
+          <t>17963425.11311239</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>5504329.0</t>
+          <t>7803829.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>8784075.8</t>
+          <t>8252460.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>8506553.8</t>
+          <t>8745649.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>8565549.34</t>
+          <t>8646425.52</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>277522</t>
+          <t>-493188</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>15312.55384128857</t>
+          <t>-89024.34543927149</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-670000.83</v>
+        <v>-662877.29</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>311.454</t>
+          <t>245.739</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.98</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-62.83</t>
+          <t>-70.36</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-86.90</t>
+          <t>-88.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17983079.02380952</t>
+          <t>17963425.11311239</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>6893754.0</t>
+          <t>5504329.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>9492182.0</t>
+          <t>8784075.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>9593018.2</t>
+          <t>8506553.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>8490905.06</t>
+          <t>8565549.34</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-100836</t>
+          <t>277522</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>139914.9870893983</t>
+          <t>15312.55384128857</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-409873.71</v>
+        <v>-670000.83</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>217.146</t>
+          <t>311.454</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,17 +10060,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,32 +10080,32 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-41.72</t>
+          <t>-62.83</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-86.90</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17983079.02380952</t>
+          <t>17963425.11311239</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4873562.0</t>
+          <t>6893754.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>10718241.8</t>
+          <t>9492182.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>12106318.1</t>
+          <t>9593018.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>8416563.16</t>
+          <t>8490905.06</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1388076</t>
+          <t>-100836</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>239876.5684125876</t>
+          <t>139914.9870893983</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-172492.16</v>
+        <v>-409873.71</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>342.425</t>
+          <t>289.28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-12.99</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>152.62</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>157.92</t>
+          <t>158.09</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.51</t>
+          <t>155.36</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-23.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.95</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>67444352.4</t>
+          <t>56961392.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>66640291.1</t>
+          <t>65462845.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>147939586.16</t>
+          <t>147489165.54</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>804061</t>
+          <t>-8501452</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12718123.77158551</t>
+          <t>-12676312.66952571</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-11824563.98</v>
+        <v>-12446351.61</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>523.223</t>
+          <t>342.425</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>153.07</t>
+          <t>152.62</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>157.86</t>
+          <t>157.92</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>155.74</t>
+          <t>155.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-125.58</t>
+          <t>-127.95</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>77542911.0</t>
+          <t>67444352.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>67555966.7</t>
+          <t>66640291.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>148067039.32</t>
+          <t>147939586.16</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>9986944</t>
+          <t>804061</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-12880589.18892824</t>
+          <t>-12718123.77158551</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-11249110.18</v>
+        <v>-11824563.98</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-17.56</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>253.617</t>
+          <t>523.223</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.37</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,17 +1871,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>153.07</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>157.78</t>
+          <t>157.86</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>155.74</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-32.26</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-125.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>75418593.0</t>
+          <t>77542911.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>69462697.8</t>
+          <t>67555966.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>147915441.16</t>
+          <t>148067039.32</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5955895</t>
+          <t>9986944</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-13177221.73576224</t>
+          <t>-12880589.18892824</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-12916861.75</v>
+        <v>-11249110.18</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>517.468</t>
+          <t>253.617</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>154.22</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>157.66</t>
+          <t>157.78</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>156.07</t>
+          <t>155.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.94</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>77078460.4</t>
+          <t>75418593.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>83740554.0</t>
+          <t>69462697.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>148438894.86</t>
+          <t>147915441.16</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-6662093</t>
+          <t>5955895</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-13224559.91433039</t>
+          <t>-13177221.73576224</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-10700633.4</v>
+        <v>-12916861.75</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>634.036</t>
+          <t>517.468</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-24.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>154.88</t>
+          <t>154.22</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>157.54</t>
+          <t>157.66</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>156.07</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.14</t>
+          <t>-121.94</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>73964298.0</t>
+          <t>77078460.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>97688090.1</t>
+          <t>83740554.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>148383127.96</t>
+          <t>148438894.86</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-23723792</t>
+          <t>-6662093</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-13683455.64394853</t>
+          <t>-13224559.91433039</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-11420753.81</v>
+        <v>-10700633.4</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>148.5</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>149.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>656.712</t>
+          <t>634.036</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.97</t>
+          <t>-24.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>154.6</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>154.88</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>157.43</t>
+          <t>157.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>156.51</t>
+          <t>156.28</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-24.10</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.63</t>
+          <t>-120.14</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>100112352.0</t>
+          <t>95173237.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>65836229.8</t>
+          <t>73964298.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>98222294.2</t>
+          <t>97688090.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>147860696.88</t>
+          <t>148383127.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-32386064</t>
+          <t>-23723792</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-14094855.97693689</t>
+          <t>-13683455.64394853</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-13899869.76</v>
+        <v>-11420753.81</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>426.802</t>
+          <t>656.712</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-38.64</t>
+          <t>-32.97</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>155.4</t>
+          <t>154.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>156.48</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>157.34</t>
+          <t>157.43</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>156.75</t>
+          <t>156.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>-24.10</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.51</t>
+          <t>-118.63</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>65986071.0</t>
+          <t>100112352.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>57569022.4</t>
+          <t>65836229.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>93825463.8</t>
+          <t>98222294.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>146775704.64</t>
+          <t>147860696.88</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-36256441</t>
+          <t>-32386064</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-14130308.01572335</t>
+          <t>-14094855.97693689</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-17474230.95</v>
+        <v>-13899869.76</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>300.495</t>
+          <t>426.802</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-38.64</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>155.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>157.32</t>
+          <t>156.48</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>157.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>156.88</t>
+          <t>156.75</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-13.95</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-117.51</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46291133.0</t>
+          <t>65986071.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>63506802.6</t>
+          <t>57569022.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>95637445.0</t>
+          <t>93825463.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>146570119.66</t>
+          <t>146775704.64</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-32130642</t>
+          <t>-36256441</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-13522322.02727396</t>
+          <t>-14130308.01572335</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-18299994.29</v>
+        <v>-17474230.95</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>398.559</t>
+          <t>300.495</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.3</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>156.2</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>158.55</t>
+          <t>157.32</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>157.02</t>
+          <t>156.88</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-15.91</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>62258697.0</t>
+          <t>46291133.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>90402647.6</t>
+          <t>63506802.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>101054998.5</t>
+          <t>95637445.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>147052834.54</t>
+          <t>146570119.66</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-10652350</t>
+          <t>-32130642</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-12653654.34228084</t>
+          <t>-13522322.02727396</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-16715913.06</v>
+        <v>-18299994.29</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>349.772</t>
+          <t>398.559</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>59.65</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>156.9</t>
+          <t>156.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>159.88</t>
+          <t>158.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>156.96</t>
+          <t>157.14</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>157.15</t>
+          <t>157.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-28.64</t>
+          <t>-15.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-115.64</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>54532896.0</t>
+          <t>62258697.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>121411882.2</t>
+          <t>90402647.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>99798952.2</t>
+          <t>101054998.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>146779920.26</t>
+          <t>147052834.54</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>21612930</t>
+          <t>-10652350</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11915061.8482831</t>
+          <t>-12653654.34228084</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-15566753.4</v>
+        <v>-16715913.06</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>158.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>382.118</t>
+          <t>349.772</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29.81</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>156.3</t>
+          <t>156.9</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>161.15</t>
+          <t>159.88</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>156.71</t>
+          <t>156.96</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>157.38</t>
+          <t>157.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-54.84</t>
+          <t>-28.64</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.52</t>
+          <t>-115.64</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>192667952.5785303</t>
+          <t>192483016.9014388</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>58776315.0</t>
+          <t>54532896.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>130608358.6</t>
+          <t>121411882.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>100613378.5</t>
+          <t>99798952.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>146823636.06</t>
+          <t>146779920.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>29994980</t>
+          <t>21612930</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11251117.92990897</t>
+          <t>-11915061.8482831</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-12541376.87</v>
+        <v>-15566753.4</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>130.298</t>
+          <t>379.722</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,37 +5765,37 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-75.17</t>
+          <t>-169.84</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-93.42</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17963425.11311239</t>
+          <t>17955259.22805755</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>10148918.0</t>
+          <t>9180056.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9267970.7</t>
+          <t>9536746.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>9823853.94</t>
+          <t>9944544.64</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>880947</t>
+          <t>-356690</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-38141.30183444001</t>
+          <t>-87719.36730254497</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-328714.05</v>
+        <v>-360398.73</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>412.554</t>
+          <t>130.298</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,72 +6065,72 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-1.21</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,64 +6196,64 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-75.17</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-92.18</t>
+          <t>-93.42</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17963425.11311239</t>
+          <t>17955259.22805755</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>9391435.0</t>
+          <t>2895510.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>12252577.6</t>
+          <t>10148918.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9667795.1</t>
+          <t>9267970.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>9822957.84</t>
+          <t>9823853.94</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2584782</t>
+          <t>880947</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>14690.10663538189</t>
+          <t>-38141.30183444001</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>295780.28</v>
+        <v>-328714.05</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>639.921</t>
+          <t>412.554</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,78 +6591,78 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-92.18</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17963425.11311239</t>
+          <t>17955259.22805755</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>11577776.6</t>
+          <t>12252577.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9216007.8</t>
+          <t>9667795.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>9691364.4</t>
+          <t>9822957.84</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2361768</t>
+          <t>2584782</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-36417.19768447067</t>
+          <t>14690.10663538189</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>481359.49</v>
+        <v>295780.28</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>446.427</t>
+          <t>639.921</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,122 +7063,122 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>22.14</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>31.31</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-91.86</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>17955259.22805755</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>14958432.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>11577776.6</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>9216007.8</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>9691364.4</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>2361768</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-36417.19768447067</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>481359.49</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-92.50</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>17963425.11311239</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>10462814.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>10425234.4</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>9338847.5</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>9424082.38</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>1086386</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>-130558.4136477165</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>132817.27</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
       <c r="BF16" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>561.564</t>
+          <t>446.427</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,74 +7358,74 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-8.78</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>11.63</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-7.31</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-1.21</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>23.25</t>
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-92.99</t>
+          <t>-92.50</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17963425.11311239</t>
+          <t>17955259.22805755</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>9893437.4</t>
+          <t>10425234.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9338756.6</t>
+          <t>9338847.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9295806.7</t>
+          <t>9424082.38</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>554680</t>
+          <t>1086386</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-178444.901985053</t>
+          <t>-130558.4136477165</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>111829.7</v>
+        <v>132817.27</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>576.54</t>
+          <t>561.564</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7884,33 +7884,33 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,57 +7920,57 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>83.26</t>
+          <t>96.08</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-93.18</t>
+          <t>-92.99</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17963425.11311239</t>
+          <t>17955259.22805755</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>13413808.0</t>
+          <t>13036399.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8387023.4</t>
+          <t>9893437.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>8939602.7</t>
+          <t>9338756.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>9062267.64</t>
+          <t>9295806.7</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-552579</t>
+          <t>554680</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-231222.1025627005</t>
+          <t>-178444.901985053</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-197887.71</v>
+        <v>111829.7</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,17 +8158,17 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>264.169</t>
+          <t>576.54</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-20.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,72 +8336,72 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>83.26</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-56.73</t>
+          <t>-15.88</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-92.91</t>
+          <t>-93.18</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>17963425.11311239</t>
+          <t>17955259.22805755</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>6017430.0</t>
+          <t>13413808.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>7083012.6</t>
+          <t>8387023.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8900627.2</t>
+          <t>8939602.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>8842829.82</t>
+          <t>9062267.64</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1817614</t>
+          <t>-552579</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-237282.9010257832</t>
+          <t>-231222.1025627005</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-673710.42</v>
+        <v>-197887.71</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>403.272</t>
+          <t>264.169</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-20.42</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,67 +8767,67 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-63.95</t>
+          <t>-56.73</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-92.91</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17963425.11311239</t>
+          <t>17955259.22805755</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>9195721.0</t>
+          <t>6017430.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>6854239.0</t>
+          <t>7083012.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>8862595.7</t>
+          <t>8900627.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>8796355.32</t>
+          <t>8842829.82</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2008356</t>
+          <t>-1817614</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-157932.4435127094</t>
+          <t>-237282.9010257832</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-536926.98</v>
+        <v>-673710.42</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>348.023</t>
+          <t>403.272</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,275 +9198,275 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
+          <t>22.92</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>22.23</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>22.01</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-63.95</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-91.90</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>17955259.22805755</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>9195721.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>6854239.0</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>8862595.7</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>8796355.32</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-2008356</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-157932.4435127094</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>-536926.98</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>51.55</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>43.72%</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>18.33</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>岱宇-運動休閒-上市</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>22.9</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-74.11</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-90.60</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>17963425.11311239</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>7803829.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>8252460.6</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>8745649.0</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>8646425.52</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>-493188</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-89024.34543927149</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>-662877.29</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>52.14</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr">
-        <is>
-          <t>43.72%</t>
-        </is>
-      </c>
-      <c r="BW21" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>18.27</t>
-        </is>
-      </c>
-      <c r="BY21" t="inlineStr">
-        <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="BZ21" t="inlineStr">
-        <is>
-          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA21" t="inlineStr">
-        <is>
-          <t>岱宇-運動休閒-上市</t>
-        </is>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>22.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>245.739</t>
+          <t>348.023</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,37 +9629,37 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -9679,27 +9679,27 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-70.36</t>
+          <t>-74.11</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-88.86</t>
+          <t>-90.60</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17963425.11311239</t>
+          <t>17955259.22805755</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>5504329.0</t>
+          <t>7803829.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>8784075.8</t>
+          <t>8252460.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>8506553.8</t>
+          <t>8745649.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>8565549.34</t>
+          <t>8646425.52</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>277522</t>
+          <t>-493188</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>15312.55384128857</t>
+          <t>-89024.34543927149</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-670000.83</v>
+        <v>-662877.29</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,42 +9797,42 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>311.454</t>
+          <t>245.739</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.98</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-62.83</t>
+          <t>-70.36</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-86.90</t>
+          <t>-88.86</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17963425.11311239</t>
+          <t>17955259.22805755</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>6893754.0</t>
+          <t>5504329.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>9492182.0</t>
+          <t>8784075.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>9593018.2</t>
+          <t>8506553.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>8490905.06</t>
+          <t>8565549.34</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-100836</t>
+          <t>277522</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>139914.9870893983</t>
+          <t>15312.55384128857</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-409873.71</v>
+        <v>-670000.83</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,42 +10228,42 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>377.931</t>
+          <t>2163.744</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>20.41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>152.2</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>158.19</t>
+          <t>158.59</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.24</t>
+          <t>155.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-13.05</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,56 +1094,56 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-130.73</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>52644238.8</t>
+          <t>114104844.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>64861349.6</t>
+          <t>94761718.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>147121902.5</t>
+          <t>152570926.34</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-12217110</t>
+          <t>19343125</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12504425.56812013</t>
+          <t>-8883764.015973106</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-11559046.51038941</t>
+          <t>11029874.52083552</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>56243740</v>
+        <v>345294824</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>289.28</t>
+          <t>377.931</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>-18.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>152.2</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>158.09</t>
+          <t>158.19</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>155.36</t>
+          <t>155.24</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-23.98</t>
+          <t>-13.05</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-130.73</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>56961392.6</t>
+          <t>52644238.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>65462845.3</t>
+          <t>64861349.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>147489165.54</t>
+          <t>147121902.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-8501452</t>
+          <t>-12217110</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-12676312.66952571</t>
+          <t>-12504425.56812013</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-12446351.60819685</t>
+          <t>-11559046.51038941</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>42758438</v>
+        <v>56243740</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>342.425</t>
+          <t>289.28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-12.99</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>152.62</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>157.92</t>
+          <t>158.09</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>155.51</t>
+          <t>155.36</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-23.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.95</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>67444352.4</t>
+          <t>56961392.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>66640291.1</t>
+          <t>65462845.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>147939586.16</t>
+          <t>147489165.54</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>804061</t>
+          <t>-8501452</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12718123.77158551</t>
+          <t>-12676312.66952571</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-11824563.97620045</t>
+          <t>-12446351.60819685</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>49619559</v>
+        <v>42758438</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>523.223</t>
+          <t>342.425</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>153.07</t>
+          <t>152.62</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>157.86</t>
+          <t>157.92</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>155.74</t>
+          <t>155.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-125.58</t>
+          <t>-127.95</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>77542911.0</t>
+          <t>67444352.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>67555966.7</t>
+          <t>66640291.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>148067039.32</t>
+          <t>147939586.16</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9986944</t>
+          <t>804061</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12880589.18892824</t>
+          <t>-12718123.77158551</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-11249110.18134128</t>
+          <t>-11824563.97620045</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>76607661</v>
+        <v>49619559</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.56</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>253.617</t>
+          <t>523.223</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.37</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,17 +2758,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>153.07</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>157.78</t>
+          <t>157.86</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>155.74</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-32.26</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-125.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>75418593.0</t>
+          <t>77542911.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>69462697.8</t>
+          <t>67555966.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>147915441.16</t>
+          <t>148067039.32</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5955895</t>
+          <t>9986944</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-13177221.73576224</t>
+          <t>-12880589.18892824</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-12916861.75363742</t>
+          <t>-11249110.18134128</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>37991796</v>
+        <v>76607661</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2956,17 +2956,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>517.468</t>
+          <t>253.617</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>154.22</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>157.66</t>
+          <t>157.78</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>156.07</t>
+          <t>155.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.94</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>77078460.4</t>
+          <t>75418593.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>83740554.0</t>
+          <t>69462697.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>148438894.86</t>
+          <t>147915441.16</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-6662093</t>
+          <t>5955895</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-13224559.91433039</t>
+          <t>-13177221.73576224</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-10700633.40143058</t>
+          <t>-12916861.75363742</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>77829509</v>
+        <v>37991796</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>634.036</t>
+          <t>517.468</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-24.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>154.88</t>
+          <t>154.22</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>157.54</t>
+          <t>157.66</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>156.07</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.14</t>
+          <t>-121.94</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>73964298.0</t>
+          <t>77078460.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>97688090.1</t>
+          <t>83740554.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>148383127.96</t>
+          <t>148438894.86</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-23723792</t>
+          <t>-6662093</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13683455.64394853</t>
+          <t>-13224559.91433039</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-11420753.81251256</t>
+          <t>-10700633.40143058</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>95173237</v>
+        <v>77829509</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>148.5</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>149.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>656.712</t>
+          <t>634.036</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.97</t>
+          <t>-24.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>154.6</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>154.88</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>157.43</t>
+          <t>157.54</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>156.51</t>
+          <t>156.28</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-24.10</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-118.63</t>
+          <t>-120.14</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>100112352.0</t>
+          <t>95173237.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>65836229.8</t>
+          <t>73964298.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>98222294.2</t>
+          <t>97688090.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>147860696.88</t>
+          <t>148383127.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-32386064</t>
+          <t>-23723792</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-14094855.97693689</t>
+          <t>-13683455.64394853</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-13899869.76361139</t>
+          <t>-11420753.81251256</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>100112352</v>
+        <v>95173237</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>426.802</t>
+          <t>656.712</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-38.64</t>
+          <t>-32.97</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>155.4</t>
+          <t>154.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>156.48</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>157.34</t>
+          <t>157.43</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>156.75</t>
+          <t>156.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>-24.10</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.51</t>
+          <t>-118.63</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>65986071.0</t>
+          <t>100112352.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>57569022.4</t>
+          <t>65836229.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>93825463.8</t>
+          <t>98222294.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>146775704.64</t>
+          <t>147860696.88</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-36256441</t>
+          <t>-32386064</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-14130308.01572335</t>
+          <t>-14094855.97693689</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-17474230.952195</t>
+          <t>-13899869.76361139</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>65986071</v>
+        <v>100112352</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>300.495</t>
+          <t>426.802</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-38.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>155.4</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>157.32</t>
+          <t>156.48</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>157.34</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>156.88</t>
+          <t>156.75</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-13.95</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-117.51</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>46291133.0</t>
+          <t>65986071.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>63506802.6</t>
+          <t>57569022.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>95637445.0</t>
+          <t>93825463.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>146570119.66</t>
+          <t>146775704.64</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-32130642</t>
+          <t>-36256441</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-13522322.02727396</t>
+          <t>-14130308.01572335</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-18299994.29473607</t>
+          <t>-17474230.952195</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>46291133</v>
+        <v>65986071</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>398.559</t>
+          <t>300.495</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,17 +5374,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>156.2</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>158.55</t>
+          <t>157.32</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>157.02</t>
+          <t>156.88</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.91</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>192327675.799569</t>
+          <t>192794841.5961263</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>62258697.0</t>
+          <t>46291133.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>90402647.6</t>
+          <t>63506802.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>101054998.5</t>
+          <t>95637445.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>147052834.54</t>
+          <t>146570119.66</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-10652350</t>
+          <t>-32130642</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-12653654.34228084</t>
+          <t>-13522322.02727396</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-16715913.05926843</t>
+          <t>-18299994.29473607</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>62258697</v>
+        <v>46291133</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>155.691</t>
+          <t>233.901</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-33.55</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,57 +5810,57 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -5870,17 +5870,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-594.38</t>
+          <t>-1514.83</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-98.14</t>
+          <t>-100.67</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17936585.81034483</t>
+          <t>17921654.97632712</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>7748634.8</t>
+          <t>5760921.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9086934.6</t>
+          <t>8669348.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>9986424.78</t>
+          <t>10064786.9</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1338299</t>
+          <t>-2908427</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-188077.4276350392</t>
+          <t>-291255.9022970037</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-740046.7594637573</t>
+          <t>-858737.5129378084</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>3305707</v>
+        <v>5019863</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>379.722</t>
+          <t>155.691</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,12 +6246,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6266,37 +6266,37 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6306,17 +6306,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-169.84</t>
+          <t>-594.38</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-98.14</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17936585.81034483</t>
+          <t>17921654.97632712</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>9180056.2</t>
+          <t>7748634.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9536746.8</t>
+          <t>9086934.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>9944544.64</t>
+          <t>9986424.78</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-356690</t>
+          <t>-1338299</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-87719.36730254497</t>
+          <t>-188077.4276350392</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-360398.7273771223</t>
+          <t>-740046.7594637573</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>8192090</v>
+        <v>3305707</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>130.298</t>
+          <t>379.722</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6697,37 +6697,37 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-75.17</t>
+          <t>-169.84</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-93.42</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17936585.81034483</t>
+          <t>17921654.97632712</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>10148918.0</t>
+          <t>9180056.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9267970.7</t>
+          <t>9536746.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>9823853.94</t>
+          <t>9944544.64</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>880947</t>
+          <t>-356690</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-38141.30183444001</t>
+          <t>-87719.36730254497</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-328714.0484184604</t>
+          <t>-360398.7273771223</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>2895510</v>
+        <v>8192090</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>412.554</t>
+          <t>130.298</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,72 +7002,72 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-5.69</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-2.39</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7133,64 +7133,64 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-75.17</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-92.18</t>
+          <t>-93.42</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17936585.81034483</t>
+          <t>17921654.97632712</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>9391435.0</t>
+          <t>2895510.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>12252577.6</t>
+          <t>10148918.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>9667795.1</t>
+          <t>9267970.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>9822957.84</t>
+          <t>9823853.94</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2584782</t>
+          <t>880947</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>14690.10663538189</t>
+          <t>-38141.30183444001</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>295780.2803945709</t>
+          <t>-328714.0484184604</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>9391435</v>
+        <v>2895510</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>639.921</t>
+          <t>412.554</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,78 +7533,78 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-92.18</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17936585.81034483</t>
+          <t>17921654.97632712</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>11577776.6</t>
+          <t>12252577.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9216007.8</t>
+          <t>9667795.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9691364.4</t>
+          <t>9822957.84</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2361768</t>
+          <t>2584782</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-36417.19768447067</t>
+          <t>14690.10663538189</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>481359.4901133813</t>
+          <t>295780.2803945709</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>14958432</v>
+        <v>9391435</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>446.427</t>
+          <t>639.921</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,127 +8010,127 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>22.14</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>31.31</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-91.86</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>17921654.97632712</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>14958432.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>11577776.6</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>9216007.8</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>9691364.4</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>2361768</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-36417.19768447067</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>481359.4901133813</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>14958432</v>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-92.50</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>17936585.81034483</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>10462814.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>10425234.4</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>9338847.5</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>9424082.38</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>1086386</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>-130558.4136477165</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>132817.2722076345</t>
-        </is>
-      </c>
-      <c r="BD18" t="n">
-        <v>10462814</v>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
       <c r="BG18" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -8183,12 +8183,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>561.564</t>
+          <t>446.427</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,74 +8310,74 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-7.78</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>11.63</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-11.37</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-2.39</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>23.25</t>
@@ -8390,12 +8390,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-92.99</t>
+          <t>-92.50</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>17936585.81034483</t>
+          <t>17921654.97632712</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>9893437.4</t>
+          <t>10425234.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>9338756.6</t>
+          <t>9338847.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>9295806.7</t>
+          <t>9424082.38</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>554680</t>
+          <t>1086386</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-178444.901985053</t>
+          <t>-130558.4136477165</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>111829.7011920083</t>
+          <t>132817.2722076345</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>13036399</v>
+        <v>10462814</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>576.54</t>
+          <t>561.564</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8756,22 +8756,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,33 +8841,33 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,57 +8877,57 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>83.26</t>
+          <t>96.08</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-93.18</t>
+          <t>-92.99</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17936585.81034483</t>
+          <t>17921654.97632712</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>13413808.0</t>
+          <t>13036399.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>8387023.4</t>
+          <t>9893437.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>8939602.7</t>
+          <t>9338756.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>9062267.64</t>
+          <t>9295806.7</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-552579</t>
+          <t>554680</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-231222.1025627005</t>
+          <t>-178444.901985053</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-197887.711015746</t>
+          <t>111829.7011920083</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>13413808</v>
+        <v>13036399</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,17 +9120,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>264.169</t>
+          <t>576.54</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-20.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,72 +9298,72 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>83.26</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-56.73</t>
+          <t>-15.88</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-92.91</t>
+          <t>-93.18</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17936585.81034483</t>
+          <t>17921654.97632712</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>6017430.0</t>
+          <t>13413808.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>7083012.6</t>
+          <t>8387023.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>8900627.2</t>
+          <t>8939602.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>8842829.82</t>
+          <t>9062267.64</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1817614</t>
+          <t>-552579</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-237282.9010257832</t>
+          <t>-231222.1025627005</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-673710.4173476892</t>
+          <t>-197887.711015746</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>6017430</v>
+        <v>13413808</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>403.272</t>
+          <t>264.169</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-20.42</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,67 +9734,67 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-63.95</t>
+          <t>-56.73</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-92.91</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17936585.81034483</t>
+          <t>17921654.97632712</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9195721.0</t>
+          <t>6017430.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>6854239.0</t>
+          <t>7083012.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>8862595.7</t>
+          <t>8900627.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>8796355.32</t>
+          <t>8842829.82</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2008356</t>
+          <t>-1817614</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-157932.4435127094</t>
+          <t>-237282.9010257832</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-536926.9829166178</t>
+          <t>-673710.4173476892</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>9195721</v>
+        <v>6017430</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>348.023</t>
+          <t>403.272</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,280 +10170,280 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
+          <t>22.92</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>22.23</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>22.01</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-63.95</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-91.90</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>17921654.97632712</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>9195721.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>6854239.0</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>8862595.7</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>8796355.32</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-2008356</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-157932.4435127094</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-536926.9829166178</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>9195721</v>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>52.02</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>43.72%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>3914</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>岱宇-運動休閒-上市</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
           <t>22.9</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-74.11</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-90.60</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>17936585.81034483</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>7803829.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>8252460.6</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>8745649.0</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>8646425.52</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-493188</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-89024.34543927149</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>-662877.2914823517</t>
-        </is>
-      </c>
-      <c r="BD23" t="n">
-        <v>7803829</v>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BT23" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="BV23" t="inlineStr">
-        <is>
-          <t>50.24</t>
-        </is>
-      </c>
-      <c r="BW23" t="inlineStr">
-        <is>
-          <t>43.72%</t>
-        </is>
-      </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="BY23" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
-      </c>
-      <c r="BZ23" t="inlineStr">
-        <is>
-          <t>3780</t>
-        </is>
-      </c>
-      <c r="CA23" t="inlineStr">
-        <is>
-          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>岱宇-運動休閒-上市</t>
-        </is>
-      </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="CD23" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>22.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2163.744</t>
+          <t>865.777</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>149.9</t>
+          <t>152.6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>152.65</t>
+          <t>153.07</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>158.59</t>
+          <t>158.92</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.37</t>
+          <t>155.41</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-126.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>114104844.4</t>
+          <t>126447355.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>94761718.7</t>
+          <t>101995133.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>152570926.34</t>
+          <t>153639291.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>19343125</t>
+          <t>24452222</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-8883764.015973106</t>
+          <t>-5818065.420489227</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>11029874.52083552</t>
+          <t>11043276.8546721</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>345294824</v>
+        <v>138320217</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>161.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>377.931</t>
+          <t>2163.744</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>20.41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>152.2</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>158.19</t>
+          <t>158.59</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>155.24</t>
+          <t>155.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-13.05</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-130.73</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>52644238.8</t>
+          <t>114104844.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>64861349.6</t>
+          <t>94761718.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>147121902.5</t>
+          <t>152570926.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-12217110</t>
+          <t>19343125</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-12504425.56812013</t>
+          <t>-8883764.015973106</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-11559046.51038941</t>
+          <t>11029874.52083552</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>56243740</v>
+        <v>345294824</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>289.28</t>
+          <t>377.931</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>-18.84</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>152.2</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>158.09</t>
+          <t>158.19</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>155.36</t>
+          <t>155.24</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-23.98</t>
+          <t>-13.05</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-130.73</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>56961392.6</t>
+          <t>52644238.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>65462845.3</t>
+          <t>64861349.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>147489165.54</t>
+          <t>147121902.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-8501452</t>
+          <t>-12217110</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12676312.66952571</t>
+          <t>-12504425.56812013</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-12446351.60819685</t>
+          <t>-11559046.51038941</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>42758438</v>
+        <v>56243740</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>342.425</t>
+          <t>289.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-12.99</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>152.62</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>157.92</t>
+          <t>158.09</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>155.51</t>
+          <t>155.36</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-23.98</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.95</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>67444352.4</t>
+          <t>56961392.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>66640291.1</t>
+          <t>65462845.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>147939586.16</t>
+          <t>147489165.54</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>804061</t>
+          <t>-8501452</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12718123.77158551</t>
+          <t>-12676312.66952571</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-11824563.97620045</t>
+          <t>-12446351.60819685</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>49619559</v>
+        <v>42758438</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>523.223</t>
+          <t>342.425</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>153.07</t>
+          <t>152.62</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>157.86</t>
+          <t>157.92</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>155.74</t>
+          <t>155.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-125.58</t>
+          <t>-127.95</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>77542911.0</t>
+          <t>67444352.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>67555966.7</t>
+          <t>66640291.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>148067039.32</t>
+          <t>147939586.16</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>9986944</t>
+          <t>804061</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12880589.18892824</t>
+          <t>-12718123.77158551</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-11249110.18134128</t>
+          <t>-11824563.97620045</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>76607661</v>
+        <v>49619559</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.56</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>253.617</t>
+          <t>523.223</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.37</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,17 +3194,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>153.07</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>157.78</t>
+          <t>157.86</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>155.74</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-32.26</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-125.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>75418593.0</t>
+          <t>77542911.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>69462697.8</t>
+          <t>67555966.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>147915441.16</t>
+          <t>148067039.32</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5955895</t>
+          <t>9986944</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-13177221.73576224</t>
+          <t>-12880589.18892824</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-12916861.75363742</t>
+          <t>-11249110.18134128</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>37991796</v>
+        <v>76607661</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>517.468</t>
+          <t>253.617</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>154.22</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>157.66</t>
+          <t>157.78</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>156.07</t>
+          <t>155.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.94</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>77078460.4</t>
+          <t>75418593.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>83740554.0</t>
+          <t>69462697.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>148438894.86</t>
+          <t>147915441.16</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-6662093</t>
+          <t>5955895</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13224559.91433039</t>
+          <t>-13177221.73576224</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-10700633.40143058</t>
+          <t>-12916861.75363742</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>77829509</v>
+        <v>37991796</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>634.036</t>
+          <t>517.468</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-24.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>154.88</t>
+          <t>154.22</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>157.54</t>
+          <t>157.66</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>156.07</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.14</t>
+          <t>-121.94</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>73964298.0</t>
+          <t>77078460.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>97688090.1</t>
+          <t>83740554.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>148383127.96</t>
+          <t>148438894.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-23723792</t>
+          <t>-6662093</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-13683455.64394853</t>
+          <t>-13224559.91433039</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-11420753.81251256</t>
+          <t>-10700633.40143058</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>95173237</v>
+        <v>77829509</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>148.5</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>149.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>656.712</t>
+          <t>634.036</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.97</t>
+          <t>-24.29</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>154.6</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>154.88</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>157.43</t>
+          <t>157.54</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>156.51</t>
+          <t>156.28</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-24.10</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-118.63</t>
+          <t>-120.14</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>100112352.0</t>
+          <t>95173237.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>65836229.8</t>
+          <t>73964298.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>98222294.2</t>
+          <t>97688090.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>147860696.88</t>
+          <t>148383127.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-32386064</t>
+          <t>-23723792</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-14094855.97693689</t>
+          <t>-13683455.64394853</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-13899869.76361139</t>
+          <t>-11420753.81251256</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>100112352</v>
+        <v>95173237</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>426.802</t>
+          <t>656.712</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-38.64</t>
+          <t>-32.97</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>155.4</t>
+          <t>154.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>156.48</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>157.34</t>
+          <t>157.43</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>156.75</t>
+          <t>156.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>-24.10</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.51</t>
+          <t>-118.63</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>65986071.0</t>
+          <t>100112352.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>57569022.4</t>
+          <t>65836229.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>93825463.8</t>
+          <t>98222294.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>146775704.64</t>
+          <t>147860696.88</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-36256441</t>
+          <t>-32386064</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-14130308.01572335</t>
+          <t>-14094855.97693689</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-17474230.952195</t>
+          <t>-13899869.76361139</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>65986071</v>
+        <v>100112352</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>300.495</t>
+          <t>426.802</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-38.64</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>866</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>155.4</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>157.32</t>
+          <t>156.48</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>157.34</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>156.88</t>
+          <t>156.75</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-13.95</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-117.51</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>192794841.5961263</t>
+          <t>192815880.9713467</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>46291133.0</t>
+          <t>65986071.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>63506802.6</t>
+          <t>57569022.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>95637445.0</t>
+          <t>93825463.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>146570119.66</t>
+          <t>146775704.64</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-32130642</t>
+          <t>-36256441</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-13522322.02727396</t>
+          <t>-14130308.01572335</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-18299994.29473607</t>
+          <t>-17474230.952195</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>46291133</v>
+        <v>65986071</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48240</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>233.901</t>
+          <t>109.472</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.55</t>
+          <t>-47.46</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,157 +5810,157 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>27.21</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-1514.83</t>
+          <t>-293.82</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-102.51</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>17901165.747851</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>4365323.8</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>8308950.7</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>10035732.7</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-3943626</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-418114.0177199567</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-1115833.652546198</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>2413449</v>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-100.67</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>17921654.97632712</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>5760921.0</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>8669348.8</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>10064786.9</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-2908427</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-291255.9022970037</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-858737.5129378084</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>5019863</v>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>岱宇</t>
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>155.691</t>
+          <t>233.901</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-33.55</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,57 +6246,57 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6306,17 +6306,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-594.38</t>
+          <t>-1514.83</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-98.14</t>
+          <t>-100.67</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17921654.97632712</t>
+          <t>17901165.747851</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>7748634.8</t>
+          <t>5760921.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9086934.6</t>
+          <t>8669348.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>9986424.78</t>
+          <t>10064786.9</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1338299</t>
+          <t>-2908427</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-188077.4276350392</t>
+          <t>-291255.9022970037</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-740046.7594637573</t>
+          <t>-858737.5129378084</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>3305707</v>
+        <v>5019863</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>379.722</t>
+          <t>155.691</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6702,37 +6702,37 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-169.84</t>
+          <t>-594.38</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-98.14</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17921654.97632712</t>
+          <t>17901165.747851</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>9180056.2</t>
+          <t>7748634.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9536746.8</t>
+          <t>9086934.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>9944544.64</t>
+          <t>9986424.78</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-356690</t>
+          <t>-1338299</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-87719.36730254497</t>
+          <t>-188077.4276350392</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-360398.7273771223</t>
+          <t>-740046.7594637573</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>8192090</v>
+        <v>3305707</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>130.298</t>
+          <t>379.722</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7133,37 +7133,37 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -7178,17 +7178,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-75.17</t>
+          <t>-169.84</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-93.42</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17921654.97632712</t>
+          <t>17901165.747851</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>10148918.0</t>
+          <t>9180056.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>9267970.7</t>
+          <t>9536746.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>9823853.94</t>
+          <t>9944544.64</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>880947</t>
+          <t>-356690</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-38141.30183444001</t>
+          <t>-87719.36730254497</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-328714.0484184604</t>
+          <t>-360398.7273771223</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>2895510</v>
+        <v>8192090</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>412.554</t>
+          <t>130.298</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,72 +7438,72 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-2.06</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7569,64 +7569,64 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-75.17</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-92.18</t>
+          <t>-93.42</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17921654.97632712</t>
+          <t>17901165.747851</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>9391435.0</t>
+          <t>2895510.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12252577.6</t>
+          <t>10148918.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9667795.1</t>
+          <t>9267970.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9822957.84</t>
+          <t>9823853.94</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2584782</t>
+          <t>880947</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>14690.10663538189</t>
+          <t>-38141.30183444001</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>295780.2803945709</t>
+          <t>-328714.0484184604</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>9391435</v>
+        <v>2895510</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>639.921</t>
+          <t>412.554</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,78 +7969,78 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-92.18</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17921654.97632712</t>
+          <t>17901165.747851</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>11577776.6</t>
+          <t>12252577.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9216007.8</t>
+          <t>9667795.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>9691364.4</t>
+          <t>9822957.84</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2361768</t>
+          <t>2584782</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-36417.19768447067</t>
+          <t>14690.10663538189</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>481359.4901133813</t>
+          <t>295780.2803945709</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>14958432</v>
+        <v>9391435</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>446.427</t>
+          <t>639.921</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,127 +8446,127 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>22.14</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>31.31</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-91.86</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>17901165.747851</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>14958432.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>11577776.6</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>9216007.8</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>9691364.4</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>2361768</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-36417.19768447067</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>481359.4901133813</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>14958432</v>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-92.50</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>17921654.97632712</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>10462814.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>10425234.4</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>9338847.5</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>9424082.38</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>1086386</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-130558.4136477165</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>132817.2722076345</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>10462814</v>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
       <c r="BG19" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -8619,12 +8619,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>561.564</t>
+          <t>446.427</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,74 +8746,74 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-5.37</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>11.63</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-7.55</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>23.25</t>
@@ -8826,12 +8826,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-92.99</t>
+          <t>-92.50</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17921654.97632712</t>
+          <t>17901165.747851</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>9893437.4</t>
+          <t>10425234.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>9338756.6</t>
+          <t>9338847.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>9295806.7</t>
+          <t>9424082.38</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>554680</t>
+          <t>1086386</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-178444.901985053</t>
+          <t>-130558.4136477165</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>111829.7011920083</t>
+          <t>132817.2722076345</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>13036399</v>
+        <v>10462814</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>576.54</t>
+          <t>561.564</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9192,22 +9192,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,33 +9277,33 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,57 +9313,57 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>83.26</t>
+          <t>96.08</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-93.18</t>
+          <t>-92.99</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17921654.97632712</t>
+          <t>17901165.747851</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>13413808.0</t>
+          <t>13036399.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>8387023.4</t>
+          <t>9893437.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>8939602.7</t>
+          <t>9338756.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>9062267.64</t>
+          <t>9295806.7</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-552579</t>
+          <t>554680</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-231222.1025627005</t>
+          <t>-178444.901985053</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-197887.711015746</t>
+          <t>111829.7011920083</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>13413808</v>
+        <v>13036399</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,24 +9556,24 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="CG21" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CH21" t="inlineStr">
         <is>
           <t>26.47</t>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>264.169</t>
+          <t>576.54</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-20.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,72 +9734,72 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>83.26</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-56.73</t>
+          <t>-15.88</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-92.91</t>
+          <t>-93.18</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17921654.97632712</t>
+          <t>17901165.747851</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>6017430.0</t>
+          <t>13413808.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>7083012.6</t>
+          <t>8387023.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>8900627.2</t>
+          <t>8939602.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>8842829.82</t>
+          <t>9062267.64</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1817614</t>
+          <t>-552579</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-237282.9010257832</t>
+          <t>-231222.1025627005</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-673710.4173476892</t>
+          <t>-197887.711015746</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>6017430</v>
+        <v>13413808</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>403.272</t>
+          <t>264.169</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-20.42</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,67 +10170,67 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-63.95</t>
+          <t>-56.73</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-92.91</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17921654.97632712</t>
+          <t>17901165.747851</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9195721.0</t>
+          <t>6017430.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>6854239.0</t>
+          <t>7083012.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>8862595.7</t>
+          <t>8900627.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>8796355.32</t>
+          <t>8842829.82</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2008356</t>
+          <t>-1817614</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-157932.4435127094</t>
+          <t>-237282.9010257832</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-536926.9829166178</t>
+          <t>-673710.4173476892</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>9195721</v>
+        <v>6017430</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>53.21</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>865.777</t>
+          <t>1550.62</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>152.6</t>
+          <t>157.1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>153.07</t>
+          <t>153.9</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>158.92</t>
+          <t>159.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.41</t>
+          <t>155.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>91.50</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.15</t>
+          <t>-121.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>126447355.6</t>
+          <t>167501275.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>101995133.3</t>
+          <t>117472813.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>153639291.3</t>
+          <t>157162554.38</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>24452222</t>
+          <t>50028461</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5818065.420489227</t>
+          <t>-1920017.357030742</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>11043276.8546721</t>
+          <t>19519246.99199092</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>138320217</v>
+        <v>254889156</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>161.5</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2163.744</t>
+          <t>865.777</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>149.9</t>
+          <t>152.6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>152.65</t>
+          <t>153.07</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>158.59</t>
+          <t>158.92</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>155.37</t>
+          <t>155.41</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-126.15</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>114104844.4</t>
+          <t>126447355.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>94761718.7</t>
+          <t>101995133.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>152570926.34</t>
+          <t>153639291.3</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>19343125</t>
+          <t>24452222</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-8883764.015973106</t>
+          <t>-5818065.420489227</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>11029874.52083552</t>
+          <t>11043276.8546721</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>345294824</v>
+        <v>138320217</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>161.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>377.931</t>
+          <t>2163.744</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>20.41</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>152.2</t>
+          <t>152.65</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>158.19</t>
+          <t>158.59</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>155.24</t>
+          <t>155.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-13.05</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-130.73</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>52644238.8</t>
+          <t>114104844.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>64861349.6</t>
+          <t>94761718.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>147121902.5</t>
+          <t>152570926.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-12217110</t>
+          <t>19343125</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12504425.56812013</t>
+          <t>-8883764.015973106</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-11559046.51038941</t>
+          <t>11029874.52083552</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>56243740</v>
+        <v>345294824</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>289.28</t>
+          <t>377.931</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>-18.84</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>152.2</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>158.09</t>
+          <t>158.19</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>155.36</t>
+          <t>155.24</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-23.98</t>
+          <t>-13.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-130.73</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>56961392.6</t>
+          <t>52644238.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>65462845.3</t>
+          <t>64861349.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>147489165.54</t>
+          <t>147121902.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-8501452</t>
+          <t>-12217110</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12676312.66952571</t>
+          <t>-12504425.56812013</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-12446351.60819685</t>
+          <t>-11559046.51038941</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>42758438</v>
+        <v>56243740</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>342.425</t>
+          <t>289.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-12.99</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>152.62</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>157.92</t>
+          <t>158.09</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>155.51</t>
+          <t>155.36</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-23.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.95</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>67444352.4</t>
+          <t>56961392.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>66640291.1</t>
+          <t>65462845.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>147939586.16</t>
+          <t>147489165.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>804061</t>
+          <t>-8501452</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12718123.77158551</t>
+          <t>-12676312.66952571</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-11824563.97620045</t>
+          <t>-12446351.60819685</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>49619559</v>
+        <v>42758438</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>523.223</t>
+          <t>342.425</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>13.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>153.07</t>
+          <t>152.62</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>157.86</t>
+          <t>157.92</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>155.74</t>
+          <t>155.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-125.58</t>
+          <t>-127.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>77542911.0</t>
+          <t>67444352.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>67555966.7</t>
+          <t>66640291.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>148067039.32</t>
+          <t>147939586.16</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>9986944</t>
+          <t>804061</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12880589.18892824</t>
+          <t>-12718123.77158551</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-11249110.18134128</t>
+          <t>-11824563.97620045</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>76607661</v>
+        <v>49619559</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.56</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>253.617</t>
+          <t>523.223</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.37</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>153.07</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>157.78</t>
+          <t>157.86</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>155.74</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-32.26</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-125.58</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>75418593.0</t>
+          <t>77542911.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>69462697.8</t>
+          <t>67555966.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>147915441.16</t>
+          <t>148067039.32</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5955895</t>
+          <t>9986944</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13177221.73576224</t>
+          <t>-12880589.18892824</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-12916861.75363742</t>
+          <t>-11249110.18134128</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>37991796</v>
+        <v>76607661</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>517.468</t>
+          <t>253.617</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>154.22</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>157.66</t>
+          <t>157.78</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>156.07</t>
+          <t>155.95</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-121.94</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>77078460.4</t>
+          <t>75418593.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>83740554.0</t>
+          <t>69462697.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>148438894.86</t>
+          <t>147915441.16</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-6662093</t>
+          <t>5955895</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-13224559.91433039</t>
+          <t>-13177221.73576224</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-10700633.40143058</t>
+          <t>-12916861.75363742</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>77829509</v>
+        <v>37991796</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4329,17 +4329,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>634.036</t>
+          <t>517.468</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-24.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.4</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>154.88</t>
+          <t>154.22</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>157.54</t>
+          <t>157.66</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>156.07</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.14</t>
+          <t>-121.94</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>73964298.0</t>
+          <t>77078460.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>97688090.1</t>
+          <t>83740554.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>148383127.96</t>
+          <t>148438894.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-23723792</t>
+          <t>-6662093</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-13683455.64394853</t>
+          <t>-13224559.91433039</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-11420753.81251256</t>
+          <t>-10700633.40143058</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>95173237</v>
+        <v>77829509</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>148.5</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>149.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>656.712</t>
+          <t>634.036</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.97</t>
+          <t>-24.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>154.6</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>154.88</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>157.43</t>
+          <t>157.54</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>156.51</t>
+          <t>156.28</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-24.10</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-118.63</t>
+          <t>-120.14</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>100112352.0</t>
+          <t>95173237.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>65836229.8</t>
+          <t>73964298.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>98222294.2</t>
+          <t>97688090.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>147860696.88</t>
+          <t>148383127.96</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-32386064</t>
+          <t>-23723792</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-14094855.97693689</t>
+          <t>-13683455.64394853</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-13899869.76361139</t>
+          <t>-11420753.81251256</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>100112352</v>
+        <v>95173237</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>426.802</t>
+          <t>656.712</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-38.64</t>
+          <t>-32.97</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>155.4</t>
+          <t>154.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>156.48</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>157.34</t>
+          <t>157.43</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>156.75</t>
+          <t>156.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>-24.10</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.51</t>
+          <t>-118.63</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>192815880.9713467</t>
+          <t>193087008.0858369</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>65986071.0</t>
+          <t>100112352.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>57569022.4</t>
+          <t>65836229.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>93825463.8</t>
+          <t>98222294.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>146775704.64</t>
+          <t>147860696.88</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-36256441</t>
+          <t>-32386064</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-14130308.01572335</t>
+          <t>-14094855.97693689</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-17474230.952195</t>
+          <t>-13899869.76361139</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>65986071</v>
+        <v>100112352</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>48240</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>109.472</t>
+          <t>125.305</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-47.46</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5825,62 +5825,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>22.56</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-293.82</t>
+          <t>-137.55</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-102.51</t>
+          <t>-103.83</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17901165.747851</t>
+          <t>17881520.03004292</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>4365323.8</t>
+          <t>4342063.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8308950.7</t>
+          <t>7245490.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>10035732.7</t>
+          <t>10018881.82</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3943626</t>
+          <t>-2903427</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-418114.0177199567</t>
+          <t>-544630.8356027965</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1115833.652546198</t>
+          <t>-1240473.333958415</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>2413449</v>
+        <v>2779206</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>233.901</t>
+          <t>109.472</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.55</t>
+          <t>-47.46</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,157 +6246,157 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>27.21</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-1514.83</t>
+          <t>-293.82</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-102.51</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>17881520.03004292</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>4365323.8</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>8308950.7</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>10035732.7</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-3943626</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-418114.0177199567</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-1115833.652546198</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>2413449</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-100.67</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>17901165.747851</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>5760921.0</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>8669348.8</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>10064786.9</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-2908427</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-291255.9022970037</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-858737.5129378084</t>
-        </is>
-      </c>
-      <c r="BD14" t="n">
-        <v>5019863</v>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>岱宇</t>
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>155.691</t>
+          <t>233.901</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-33.55</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,57 +6682,57 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-594.38</t>
+          <t>-1514.83</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-98.14</t>
+          <t>-100.67</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17901165.747851</t>
+          <t>17881520.03004292</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>7748634.8</t>
+          <t>5760921.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9086934.6</t>
+          <t>8669348.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>9986424.78</t>
+          <t>10064786.9</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1338299</t>
+          <t>-2908427</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-188077.4276350392</t>
+          <t>-291255.9022970037</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-740046.7594637573</t>
+          <t>-858737.5129378084</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>3305707</v>
+        <v>5019863</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>379.722</t>
+          <t>155.691</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,37 +7138,37 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7178,17 +7178,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-169.84</t>
+          <t>-594.38</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-98.14</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17901165.747851</t>
+          <t>17881520.03004292</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>9180056.2</t>
+          <t>7748634.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>9536746.8</t>
+          <t>9086934.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>9944544.64</t>
+          <t>9986424.78</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-356690</t>
+          <t>-1338299</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-87719.36730254497</t>
+          <t>-188077.4276350392</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-360398.7273771223</t>
+          <t>-740046.7594637573</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>8192090</v>
+        <v>3305707</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,17 +7311,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>130.298</t>
+          <t>379.722</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7569,37 +7569,37 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -7614,17 +7614,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-75.17</t>
+          <t>-169.84</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-93.42</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17901165.747851</t>
+          <t>17881520.03004292</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>10148918.0</t>
+          <t>9180056.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9267970.7</t>
+          <t>9536746.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9823853.94</t>
+          <t>9944544.64</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>880947</t>
+          <t>-356690</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-38141.30183444001</t>
+          <t>-87719.36730254497</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-328714.0484184604</t>
+          <t>-360398.7273771223</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>2895510</v>
+        <v>8192090</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>412.554</t>
+          <t>130.298</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,72 +7874,72 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,64 +8005,64 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-75.17</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-92.18</t>
+          <t>-93.42</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17901165.747851</t>
+          <t>17881520.03004292</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>9391435.0</t>
+          <t>2895510.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12252577.6</t>
+          <t>10148918.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9667795.1</t>
+          <t>9267970.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>9822957.84</t>
+          <t>9823853.94</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2584782</t>
+          <t>880947</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>14690.10663538189</t>
+          <t>-38141.30183444001</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>295780.2803945709</t>
+          <t>-328714.0484184604</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>9391435</v>
+        <v>2895510</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,17 +8183,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>639.921</t>
+          <t>412.554</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,78 +8405,78 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8486,12 +8486,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-92.18</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>17901165.747851</t>
+          <t>17881520.03004292</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>11577776.6</t>
+          <t>12252577.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>9216007.8</t>
+          <t>9667795.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>9691364.4</t>
+          <t>9822957.84</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2361768</t>
+          <t>2584782</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-36417.19768447067</t>
+          <t>14690.10663538189</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>481359.4901133813</t>
+          <t>295780.2803945709</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>14958432</v>
+        <v>9391435</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,17 +8619,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>446.427</t>
+          <t>639.921</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,127 +8882,127 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>22.14</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>31.31</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-91.86</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>17881520.03004292</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>14958432.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>11577776.6</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>9216007.8</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>9691364.4</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>2361768</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-36417.19768447067</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>481359.4901133813</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>14958432</v>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-92.50</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>17901165.747851</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>10462814.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>10425234.4</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>9338847.5</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>9424082.38</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>1086386</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-130558.4136477165</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>132817.2722076345</t>
-        </is>
-      </c>
-      <c r="BD20" t="n">
-        <v>10462814</v>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
       <c r="BG20" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -9055,12 +9055,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>561.564</t>
+          <t>446.427</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,74 +9182,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-5.37</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>11.63</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-5.15</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>23.25</t>
@@ -9262,12 +9262,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-92.99</t>
+          <t>-92.50</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17901165.747851</t>
+          <t>17881520.03004292</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>9893437.4</t>
+          <t>10425234.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9338756.6</t>
+          <t>9338847.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>9295806.7</t>
+          <t>9424082.38</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>554680</t>
+          <t>1086386</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-178444.901985053</t>
+          <t>-130558.4136477165</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>111829.7011920083</t>
+          <t>132817.2722076345</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>13036399</v>
+        <v>10462814</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>576.54</t>
+          <t>561.564</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9633,17 +9633,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9713,33 +9713,33 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,57 +9749,57 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>83.26</t>
+          <t>96.08</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-93.18</t>
+          <t>-92.99</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17901165.747851</t>
+          <t>17881520.03004292</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>13413808.0</t>
+          <t>13036399.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>8387023.4</t>
+          <t>9893437.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>8939602.7</t>
+          <t>9338756.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>9062267.64</t>
+          <t>9295806.7</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-552579</t>
+          <t>554680</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-231222.1025627005</t>
+          <t>-178444.901985053</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-197887.711015746</t>
+          <t>111829.7011920083</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>13413808</v>
+        <v>13036399</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9992,17 +9992,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>264.169</t>
+          <t>576.54</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-20.42</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,72 +10170,72 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>83.26</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-56.73</t>
+          <t>-15.88</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-92.91</t>
+          <t>-93.18</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17901165.747851</t>
+          <t>17881520.03004292</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>6017430.0</t>
+          <t>13413808.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>7083012.6</t>
+          <t>8387023.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>8900627.2</t>
+          <t>8939602.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>8842829.82</t>
+          <t>9062267.64</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1817614</t>
+          <t>-552579</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-237282.9010257832</t>
+          <t>-231222.1025627005</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-673710.4173476892</t>
+          <t>-197887.711015746</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>6017430</v>
+        <v>13413808</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>157.1</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>153.9</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>159.48</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>159.48</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>254889156.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>167501275.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>167501275</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>117472813.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>157162554.38</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>157162554.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>19519246.99199092</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>254889156</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>254889156.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>152.6</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>153.07</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>158.92</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>153.07</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>158.92</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>138320217.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>126447355.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>126447355.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>101995133.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>153639291.3</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>153639291.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>11043276.8546721</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>138320217</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>138320217.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>149.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>152.65</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>158.59</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>152.65</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>158.59</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>345294824.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>114104844.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>114104844.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>94761718.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>152570926.34</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>152570926.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>11029874.52083552</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>345294824</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>345294824.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>147.5</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>152.2</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>158.19</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>152.2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>158.19</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>56243740.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>52644238.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>52644238.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>64861349.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>147121902.5</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>147121902.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-11559046.51038941</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>56243740</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>56243740.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>147.3</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>152.38</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>158.09</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>158.09</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>42758438.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>56961392.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>56961392.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>65462845.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>147489165.54</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>147489165.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-12446351.60819685</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>42758438</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>42758438.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>147.6</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>152.62</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>157.92</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>152.62</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>157.92</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>49619559.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>67444352.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>67444352.40000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>66640291.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>147939586.16</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>147939586.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-11824563.97620045</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>49619559</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>49619559.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>148.8</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>153.07</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>157.86</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>153.07</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>157.86</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>76607661.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>77542911.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>77542911</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>67555966.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>148067039.32</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>148067039.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-11249110.18134128</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>76607661</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>76607661.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>150.5</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>153.8</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>157.78</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>153.8</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>157.78</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>37991796.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>75418593.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>75418593</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>69462697.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>147915441.16</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>147915441.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-12916861.75363742</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>37991796</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>37991796.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>151.4</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>154.22</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>157.66</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>154.22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>157.66</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>77829509.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>77078460.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>77078460.40000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>83740554.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>148438894.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>148438894.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-10700633.40143058</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>77829509</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>77829509.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>153.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>154.88</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>157.54</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>154.88</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>157.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>95173237.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>73964298.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>73964298</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>97688090.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>148383127.96</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>148383127.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-11420753.81251256</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>95173237</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>95173237.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>154.6</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>155.72</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>157.43</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>155.72</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>157.43</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>100112352.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>65836229.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>65836229.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>98222294.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>147860696.88</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>147860696.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-13899869.76361139</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>100112352</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>100112352.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>21.86</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>22.55</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2779206.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>4342063.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>4342063</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>7245490.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>10018881.82</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>10018881.82</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1240473.333958415</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2779206</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2779206.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>21.77</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>22.62</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>22.52</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2413449.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>4365323.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>4365323.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>8308950.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>10035732.7</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>10035732.7</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1115833.652546198</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2413449</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>21.76</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>22.66</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>22.49</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>5019863.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>5760921.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>5760921</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>8669348.8</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>10064786.9</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>10064786.9</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-858737.5129378084</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>5019863</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>5019863.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>22.1</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>22.74</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>22.48</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>22.48</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>3305707.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>7748634.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>7748634.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>9086934.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>9986424.78</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>9986424.779999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-740046.7594637573</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>3305707</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>3305707.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>22.59</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>22.49</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>8192090.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>9180056.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>9180056.199999999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>9536746.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>9944544.64</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>9944544.640000001</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-360398.7273771223</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>8192090</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>8192090.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>22.96</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>22.96</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>22.49</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2895510.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>10148918.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>10148918</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>9267970.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>9823853.94</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>9823853.939999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-328714.0484184604</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2895510</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2895510.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>23.28</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>23.08</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>22.48</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>22.48</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>9391435.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>12252577.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>12252577.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>9667795.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>9822957.84</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>9822957.84</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>295780.2803945709</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>9391435</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>9391435.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>23.39</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>23.13</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>22.46</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>14958432.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>11577776.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>11577776.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>9216007.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>9691364.4</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>9691364.4</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>481359.4901133813</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>14958432</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>14958432.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>23.26</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>23.09</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>22.4</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>10462814.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>10425234.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>10425234.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>9338847.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>9424082.38</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>9424082.380000001</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>132817.2722076345</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>10462814</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>10462814.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>23.07</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>23.05</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>22.35</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>13036399.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>9893437.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>9893437.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>9338756.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>9295806.7</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>9295806.699999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>111829.7011920083</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>13036399</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>13036399.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>22.87</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>22.3</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>13413808.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>8387023.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>8387023.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>8939602.7</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>9062267.64</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>9062267.640000001</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-197887.711015746</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>13413808</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>13413808.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1550.62</t>
+          <t>644.622</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>51.95</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>157.1</t>
+          <t>160.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>153.9</v>
+        <v>154.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>159.48</v>
+        <v>159.94</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.59</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>91.50</t>
+          <t>130.50</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.28</t>
+          <t>-116.04</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>254889156.0</t>
+          <t>105803270.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>167501275</v>
+        <v>180110241.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>117472813.7</t>
+          <t>118535817.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>157162554.38</v>
+        <v>157797617.5</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>50028461</t>
+          <t>61574424</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1920017.357030742</t>
+          <t>495831.9999454175</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>19519246.99199092</t>
+          <t>13783003.46331429</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>254889156.0</t>
+          <t>105803270.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>159.5</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>865.777</t>
+          <t>1550.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>152.6</t>
+          <t>157.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>153.07</v>
+        <v>153.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>158.92</v>
+        <v>159.48</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>155.41</t>
+          <t>155.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>91.50</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.15</t>
+          <t>-121.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>126447355.6</v>
+        <v>167501275</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>101995133.3</t>
+          <t>117472813.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>153639291.3</v>
+        <v>157162554.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>24452222</t>
+          <t>50028461</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5818065.420489227</t>
+          <t>-1920017.357030742</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>11043276.8546721</t>
+          <t>19519246.99199092</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>161.5</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2163.744</t>
+          <t>865.777</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>149.9</t>
+          <t>152.6</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>152.65</v>
+        <v>153.07</v>
       </c>
       <c r="AN4" t="n">
-        <v>158.59</v>
+        <v>158.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>155.37</t>
+          <t>155.41</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-126.15</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>114104844.4</v>
+        <v>126447355.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>94761718.7</t>
+          <t>101995133.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>152570926.34</v>
+        <v>153639291.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>19343125</t>
+          <t>24452222</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-8883764.015973106</t>
+          <t>-5818065.420489227</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>11029874.52083552</t>
+          <t>11043276.8546721</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>161.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>377.931</t>
+          <t>2163.744</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>20.41</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>152.2</v>
+        <v>152.65</v>
       </c>
       <c r="AN5" t="n">
-        <v>158.19</v>
+        <v>158.59</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>155.24</t>
+          <t>155.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-13.05</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-130.73</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>52644238.8</v>
+        <v>114104844.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>64861349.6</t>
+          <t>94761718.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>147121902.5</v>
+        <v>152570926.34</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-12217110</t>
+          <t>19343125</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12504425.56812013</t>
+          <t>-8883764.015973106</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-11559046.51038941</t>
+          <t>11029874.52083552</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>289.28</t>
+          <t>377.931</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>-18.84</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>152.38</v>
+        <v>152.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>158.09</v>
+        <v>158.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>155.36</t>
+          <t>155.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-23.98</t>
+          <t>-13.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-130.73</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>56961392.6</v>
+        <v>52644238.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>65462845.3</t>
+          <t>64861349.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>147489165.54</v>
+        <v>147121902.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-8501452</t>
+          <t>-12217110</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12676312.66952571</t>
+          <t>-12504425.56812013</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-12446351.60819685</t>
+          <t>-11559046.51038941</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>342.425</t>
+          <t>289.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-12.99</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>152.62</v>
+        <v>152.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>157.92</v>
+        <v>158.09</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>155.51</t>
+          <t>155.36</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-23.98</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.95</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>67444352.40000001</v>
+        <v>56961392.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>66640291.1</t>
+          <t>65462845.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>147939586.16</v>
+        <v>147489165.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>804061</t>
+          <t>-8501452</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12718123.77158551</t>
+          <t>-12676312.66952571</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-11824563.97620045</t>
+          <t>-12446351.60819685</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>523.223</t>
+          <t>342.425</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>153.07</v>
+        <v>152.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>157.86</v>
+        <v>157.92</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>155.74</t>
+          <t>155.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-125.58</t>
+          <t>-127.95</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>77542911</v>
+        <v>67444352.40000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>67555966.7</t>
+          <t>66640291.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>148067039.32</v>
+        <v>147939586.16</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>9986944</t>
+          <t>804061</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12880589.18892824</t>
+          <t>-12718123.77158551</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-11249110.18134128</t>
+          <t>-11824563.97620045</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.56</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>253.617</t>
+          <t>523.223</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.37</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>153.8</v>
+        <v>153.07</v>
       </c>
       <c r="AN9" t="n">
-        <v>157.78</v>
+        <v>157.86</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>155.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-32.26</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-125.58</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>75418593</v>
+        <v>77542911</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>69462697.8</t>
+          <t>67555966.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>147915441.16</v>
+        <v>148067039.32</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5955895</t>
+          <t>9986944</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-13177221.73576224</t>
+          <t>-12880589.18892824</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-12916861.75363742</t>
+          <t>-11249110.18134128</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>517.468</t>
+          <t>253.617</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>154.22</v>
+        <v>153.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>157.66</v>
+        <v>157.78</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>156.07</t>
+          <t>155.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-121.94</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>77078460.40000001</v>
+        <v>75418593</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>83740554.0</t>
+          <t>69462697.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>148438894.86</v>
+        <v>147915441.16</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-6662093</t>
+          <t>5955895</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-13224559.91433039</t>
+          <t>-13177221.73576224</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-10700633.40143058</t>
+          <t>-12916861.75363742</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>634.036</t>
+          <t>517.468</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-24.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>154.88</v>
+        <v>154.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>157.54</v>
+        <v>157.66</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>156.07</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.14</t>
+          <t>-121.94</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>73964298</v>
+        <v>77078460.40000001</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>97688090.1</t>
+          <t>83740554.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>148383127.96</v>
+        <v>148438894.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-23723792</t>
+          <t>-6662093</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-13683455.64394853</t>
+          <t>-13224559.91433039</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-11420753.81251256</t>
+          <t>-10700633.40143058</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>148.5</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>149.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>656.712</t>
+          <t>634.036</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.97</t>
+          <t>-24.29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>154.6</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>155.72</v>
+        <v>154.88</v>
       </c>
       <c r="AN12" t="n">
-        <v>157.43</v>
+        <v>157.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>156.51</t>
+          <t>156.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-24.10</t>
+          <t>-29.99</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.63</t>
+          <t>-120.14</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>193087008.0858369</t>
+          <t>193037890.7957143</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>100112352.0</t>
+          <t>95173237.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>65836229.8</v>
+        <v>73964298</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>98222294.2</t>
+          <t>97688090.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>147860696.88</v>
+        <v>148383127.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-32386064</t>
+          <t>-23723792</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-14094855.97693689</t>
+          <t>-13683455.64394853</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-13899869.76361139</t>
+          <t>-11420753.81251256</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>100112352.0</t>
+          <t>95173237.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>196.646</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>125.305</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-40.07</t>
+          <t>-44.01</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,58 +5749,58 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>22.56</v>
+        <v>22.53</v>
       </c>
       <c r="AN13" t="n">
-        <v>22.55</v>
+        <v>22.58</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-137.55</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-103.83</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17881520.03004292</t>
+          <t>17865248.04857143</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2779206.0</t>
+          <t>4327422.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>4342063</v>
+        <v>3569129.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7245490.5</t>
+          <t>6374592.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>10018881.82</v>
+        <v>10085156.06</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2903427</t>
+          <t>-2805463</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-544630.8356027965</t>
+          <t>-642471.1805251366</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1240473.333958415</t>
+          <t>-1180593.077598007</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2779206.0</t>
+          <t>4327422.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>109.472</t>
+          <t>125.305</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-47.46</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>22.62</v>
+        <v>22.56</v>
       </c>
       <c r="AN14" t="n">
-        <v>22.52</v>
+        <v>22.55</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-293.82</t>
+          <t>-137.55</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-102.51</t>
+          <t>-103.83</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17881520.03004292</t>
+          <t>17865248.04857143</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>4365323.8</v>
+        <v>4342063</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>8308950.7</t>
+          <t>7245490.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>10035732.7</v>
+        <v>10018881.82</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-3943626</t>
+          <t>-2903427</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-418114.0177199567</t>
+          <t>-544630.8356027965</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1115833.652546198</t>
+          <t>-1240473.333958415</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,24 +6426,24 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>22.45</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>22.35</t>
         </is>
       </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
       <c r="CH14" t="inlineStr">
         <is>
           <t>26.47</t>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>233.901</t>
+          <t>109.472</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.55</t>
+          <t>-47.46</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,146 +6609,146 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>27.21</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>22.66</v>
+        <v>22.62</v>
       </c>
       <c r="AN15" t="n">
-        <v>22.49</v>
+        <v>22.52</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-1514.83</t>
+          <t>-293.82</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-102.51</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>17865248.04857143</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>4365323.8</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>8308950.7</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>10035732.7</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-3943626</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-418114.0177199567</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-1115833.652546198</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-100.67</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>17881520.03004292</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>5760921</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>8669348.8</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>10064786.9</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-2908427</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-291255.9022970037</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-858737.5129378084</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>岱宇</t>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>155.691</t>
+          <t>233.901</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-33.55</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,49 +7039,49 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>22.74</v>
+        <v>22.66</v>
       </c>
       <c r="AN16" t="n">
-        <v>22.48</v>
+        <v>22.49</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7090,17 +7090,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-594.38</t>
+          <t>-1514.83</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-98.14</t>
+          <t>-100.67</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17881520.03004292</t>
+          <t>17865248.04857143</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>7748634.8</v>
+        <v>5760921</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>9086934.6</t>
+          <t>8669348.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>9986424.779999999</v>
+        <v>10064786.9</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1338299</t>
+          <t>-2908427</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-188077.4276350392</t>
+          <t>-291255.9022970037</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-740046.7594637573</t>
+          <t>-858737.5129378084</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,42 +7201,42 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>379.722</t>
+          <t>155.691</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,34 +7484,34 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>22.86</v>
+        <v>22.74</v>
       </c>
       <c r="AN17" t="n">
-        <v>22.49</v>
+        <v>22.48</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-169.84</t>
+          <t>-594.38</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-98.14</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17881520.03004292</t>
+          <t>17865248.04857143</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>9180056.199999999</v>
+        <v>7748634.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9536746.8</t>
+          <t>9086934.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>9944544.640000001</v>
+        <v>9986424.779999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-356690</t>
+          <t>-1338299</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-87719.36730254497</t>
+          <t>-188077.4276350392</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-360398.7273771223</t>
+          <t>-740046.7594637573</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>130.298</t>
+          <t>379.722</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,36 +7909,36 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>22.96</v>
+        <v>22.86</v>
       </c>
       <c r="AN18" t="n">
         <v>22.49</v>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-75.17</t>
+          <t>-169.84</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-93.42</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17881520.03004292</t>
+          <t>17865248.04857143</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>10148918</v>
+        <v>9180056.199999999</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9267970.7</t>
+          <t>9536746.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>9823853.939999999</v>
+        <v>9944544.640000001</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>880947</t>
+          <t>-356690</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-38141.30183444001</t>
+          <t>-87719.36730254497</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-328714.0484184604</t>
+          <t>-360398.7273771223</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>412.554</t>
+          <t>130.298</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,72 +8208,72 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,194 +8339,194 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>22.96</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-75.17</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-93.42</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>17865248.04857143</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>2895510.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>10148918</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>9267970.7</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>9823853.939999999</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>880947</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-38141.30183444001</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-328714.0484184604</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2895510.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>-2.23</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>23.08</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>22.48</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-16.29</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-92.18</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>17881520.03004292</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>9391435.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>12252577.6</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>9667795.1</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>9822957.84</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>2584782</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>14690.10663538189</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>295780.2803945709</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>9391435.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8606,14 +8606,14 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>639.921</t>
+          <t>412.554</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,22 +8733,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -8759,49 +8759,49 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>23.13</v>
+        <v>23.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>22.46</v>
+        <v>22.48</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-92.18</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17881520.03004292</t>
+          <t>17865248.04857143</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>11577776.6</v>
+        <v>12252577.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>9216007.8</t>
+          <t>9667795.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>9691364.4</v>
+        <v>9822957.84</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2361768</t>
+          <t>2584782</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-36417.19768447067</t>
+          <t>14690.10663538189</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>481359.4901133813</t>
+          <t>295780.2803945709</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>446.427</t>
+          <t>639.921</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>23.09</v>
+        <v>23.13</v>
       </c>
       <c r="AN21" t="n">
-        <v>22.4</v>
+        <v>22.46</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>31.31</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-92.50</t>
+          <t>-91.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17881520.03004292</t>
+          <t>17865248.04857143</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>10462814.0</t>
+          <t>14958432.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>10425234.4</v>
+        <v>11577776.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9338847.5</t>
+          <t>9216007.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>9424082.380000001</v>
+        <v>9691364.4</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1086386</t>
+          <t>2361768</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-130558.4136477165</t>
+          <t>-36417.19768447067</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>132817.2722076345</t>
+          <t>481359.4901133813</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>10462814.0</t>
+          <t>14958432.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>561.564</t>
+          <t>446.427</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,74 +9498,74 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-6.08</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>11.63</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-5.15</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>23.25</t>
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>23.05</v>
+        <v>23.09</v>
       </c>
       <c r="AN22" t="n">
-        <v>22.35</v>
+        <v>22.4</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-92.99</t>
+          <t>-92.50</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17881520.03004292</t>
+          <t>17865248.04857143</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>9893437.4</v>
+        <v>10425234.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>9338756.6</t>
+          <t>9338847.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>9295806.699999999</v>
+        <v>9424082.380000001</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>554680</t>
+          <t>1086386</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-178444.901985053</t>
+          <t>-130558.4136477165</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>111829.7011920083</t>
+          <t>132817.2722076345</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9896,14 +9896,14 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>576.54</t>
+          <t>561.564</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9938,22 +9938,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10023,22 +10023,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,53 +10059,53 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>83.26</t>
+          <t>96.08</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>23</v>
+        <v>23.05</v>
       </c>
       <c r="AN23" t="n">
-        <v>22.3</v>
+        <v>22.35</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-93.18</t>
+          <t>-92.99</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,48 +10130,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17881520.03004292</t>
+          <t>17865248.04857143</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>13413808.0</t>
+          <t>13036399.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>8387023.4</v>
+        <v>9893437.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>8939602.7</t>
+          <t>9338756.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>9062267.640000001</v>
+        <v>9295806.699999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-552579</t>
+          <t>554680</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-231222.1025627005</t>
+          <t>-178444.901985053</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-197887.711015746</t>
+          <t>111829.7011920083</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>13413808.0</t>
+          <t>13036399.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,24 +10296,24 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CH23" t="inlineStr">
         <is>
           <t>26.47</t>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>644.622</t>
+          <t>801.259</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>51.95</t>
+          <t>57.44</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>160.1</t>
+          <t>162.6</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>154.32</v>
+        <v>154.43</v>
       </c>
       <c r="AN2" t="n">
-        <v>159.94</v>
+        <v>160.4</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>155.79</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>130.50</t>
+          <t>184.19</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-116.04</t>
+          <t>-110.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>105803270.0</t>
+          <t>129373440.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>180110241.4</v>
+        <v>194736181.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>118535817.0</t>
+          <t>123690210.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>157797617.5</v>
+        <v>158323451.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>61574424</t>
+          <t>71045971</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>495831.9999454175</t>
+          <t>2141214.870208863</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>13783003.46331429</t>
+          <t>11190820.65665781</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>105803270.0</t>
+          <t>129373440.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1550.62</t>
+          <t>644.622</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>51.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>157.1</t>
+          <t>160.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>153.9</v>
+        <v>154.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>159.48</v>
+        <v>159.94</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>155.59</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>91.50</t>
+          <t>130.50</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.28</t>
+          <t>-116.04</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>254889156.0</t>
+          <t>105803270.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>167501275</v>
+        <v>180110241.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>117472813.7</t>
+          <t>118535817.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>157162554.38</v>
+        <v>157797617.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>50028461</t>
+          <t>61574424</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1920017.357030742</t>
+          <t>495831.9999454175</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>19519246.99199092</t>
+          <t>13783003.46331429</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>254889156.0</t>
+          <t>105803270.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>159.5</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>865.777</t>
+          <t>1550.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>152.6</t>
+          <t>157.1</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>153.07</v>
+        <v>153.9</v>
       </c>
       <c r="AN4" t="n">
-        <v>158.92</v>
+        <v>159.48</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>155.41</t>
+          <t>155.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>91.50</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-126.15</t>
+          <t>-121.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>126447355.6</v>
+        <v>167501275</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>101995133.3</t>
+          <t>117472813.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>153639291.3</v>
+        <v>157162554.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>24452222</t>
+          <t>50028461</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5818065.420489227</t>
+          <t>-1920017.357030742</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>11043276.8546721</t>
+          <t>19519246.99199092</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>161.5</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2163.744</t>
+          <t>865.777</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>149.9</t>
+          <t>152.6</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>152.65</v>
+        <v>153.07</v>
       </c>
       <c r="AN5" t="n">
-        <v>158.59</v>
+        <v>158.92</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>155.37</t>
+          <t>155.41</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-126.15</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>114104844.4</v>
+        <v>126447355.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>94761718.7</t>
+          <t>101995133.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>152570926.34</v>
+        <v>153639291.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>19343125</t>
+          <t>24452222</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8883764.015973106</t>
+          <t>-5818065.420489227</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>11029874.52083552</t>
+          <t>11043276.8546721</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>161.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>377.931</t>
+          <t>2163.744</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>20.41</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>152.2</v>
+        <v>152.65</v>
       </c>
       <c r="AN6" t="n">
-        <v>158.19</v>
+        <v>158.59</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>155.24</t>
+          <t>155.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-13.05</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-130.73</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>52644238.8</v>
+        <v>114104844.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>64861349.6</t>
+          <t>94761718.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>147121902.5</v>
+        <v>152570926.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-12217110</t>
+          <t>19343125</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12504425.56812013</t>
+          <t>-8883764.015973106</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-11559046.51038941</t>
+          <t>11029874.52083552</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>289.28</t>
+          <t>377.931</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>-18.84</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>152.38</v>
+        <v>152.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>158.09</v>
+        <v>158.19</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>155.36</t>
+          <t>155.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-23.98</t>
+          <t>-13.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-130.73</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>56961392.6</v>
+        <v>52644238.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>65462845.3</t>
+          <t>64861349.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>147489165.54</v>
+        <v>147121902.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-8501452</t>
+          <t>-12217110</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12676312.66952571</t>
+          <t>-12504425.56812013</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-12446351.60819685</t>
+          <t>-11559046.51038941</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>342.425</t>
+          <t>289.28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-12.99</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>152.62</v>
+        <v>152.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>157.92</v>
+        <v>158.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>155.51</t>
+          <t>155.36</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-23.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.95</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>67444352.40000001</v>
+        <v>56961392.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>66640291.1</t>
+          <t>65462845.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>147939586.16</v>
+        <v>147489165.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>804061</t>
+          <t>-8501452</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12718123.77158551</t>
+          <t>-12676312.66952571</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-11824563.97620045</t>
+          <t>-12446351.60819685</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>523.223</t>
+          <t>342.425</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>153.07</v>
+        <v>152.62</v>
       </c>
       <c r="AN9" t="n">
-        <v>157.86</v>
+        <v>157.92</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>155.74</t>
+          <t>155.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-125.58</t>
+          <t>-127.95</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>77542911</v>
+        <v>67444352.40000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>67555966.7</t>
+          <t>66640291.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>148067039.32</v>
+        <v>147939586.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9986944</t>
+          <t>804061</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12880589.18892824</t>
+          <t>-12718123.77158551</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-11249110.18134128</t>
+          <t>-11824563.97620045</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.56</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>253.617</t>
+          <t>523.223</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.37</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>153.8</v>
+        <v>153.07</v>
       </c>
       <c r="AN10" t="n">
-        <v>157.78</v>
+        <v>157.86</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>155.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-32.26</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-125.58</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>75418593</v>
+        <v>77542911</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>69462697.8</t>
+          <t>67555966.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>147915441.16</v>
+        <v>148067039.32</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5955895</t>
+          <t>9986944</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-13177221.73576224</t>
+          <t>-12880589.18892824</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-12916861.75363742</t>
+          <t>-11249110.18134128</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>517.468</t>
+          <t>253.617</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>154.22</v>
+        <v>153.8</v>
       </c>
       <c r="AN11" t="n">
-        <v>157.66</v>
+        <v>157.78</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>156.07</t>
+          <t>155.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-121.94</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>77078460.40000001</v>
+        <v>75418593</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>83740554.0</t>
+          <t>69462697.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>148438894.86</v>
+        <v>147915441.16</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-6662093</t>
+          <t>5955895</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-13224559.91433039</t>
+          <t>-13177221.73576224</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-10700633.40143058</t>
+          <t>-12916861.75363742</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>634.036</t>
+          <t>517.468</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-24.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>154.88</v>
+        <v>154.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>157.54</v>
+        <v>157.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>156.07</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-32.75</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.14</t>
+          <t>-121.94</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>193037890.7957143</t>
+          <t>193039349.0970043</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>73964298</v>
+        <v>77078460.40000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>97688090.1</t>
+          <t>83740554.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>148383127.96</v>
+        <v>148438894.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-23723792</t>
+          <t>-6662093</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-13683455.64394853</t>
+          <t>-13224559.91433039</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-11420753.81251256</t>
+          <t>-10700633.40143058</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>95173237.0</t>
+          <t>77829509.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-15.86</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>148.5</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>149.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>196.646</t>
+          <t>143.091</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-37.22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>65.31</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>22.53</v>
+        <v>22.51</v>
       </c>
       <c r="AN13" t="n">
-        <v>22.58</v>
+        <v>22.61</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-42.77</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17865248.04857143</t>
+          <t>17846581.03352354</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4327422.0</t>
+          <t>3186447.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3569129.4</v>
+        <v>3545277.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>6374592.8</t>
+          <t>5646956.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>10085156.06</v>
+        <v>9899078.18</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2805463</t>
+          <t>-2101678</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-642471.1805251366</t>
+          <t>-727434.8752452343</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1180593.077598007</t>
+          <t>-1194735.196205772</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>4327422.0</t>
+          <t>3186447.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>125.305</t>
+          <t>196.646</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-40.07</t>
+          <t>-44.01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,58 +6179,58 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>22.56</v>
+        <v>22.53</v>
       </c>
       <c r="AN14" t="n">
-        <v>22.55</v>
+        <v>22.58</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-137.55</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-103.83</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17865248.04857143</t>
+          <t>17846581.03352354</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2779206.0</t>
+          <t>4327422.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>4342063</v>
+        <v>3569129.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7245490.5</t>
+          <t>6374592.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>10018881.82</v>
+        <v>10085156.06</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2903427</t>
+          <t>-2805463</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-544630.8356027965</t>
+          <t>-642471.1805251366</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1240473.333958415</t>
+          <t>-1180593.077598007</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2779206.0</t>
+          <t>4327422.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>109.472</t>
+          <t>125.305</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-47.46</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>22.62</v>
+        <v>22.56</v>
       </c>
       <c r="AN15" t="n">
-        <v>22.52</v>
+        <v>22.55</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-293.82</t>
+          <t>-137.55</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-102.51</t>
+          <t>-103.83</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17865248.04857143</t>
+          <t>17846581.03352354</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>4365323.8</v>
+        <v>4342063</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8308950.7</t>
+          <t>7245490.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>10035732.7</v>
+        <v>10018881.82</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-3943626</t>
+          <t>-2903427</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-418114.0177199567</t>
+          <t>-544630.8356027965</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1115833.652546198</t>
+          <t>-1240473.333958415</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>233.901</t>
+          <t>109.472</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.55</t>
+          <t>-47.46</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,146 +7039,146 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>27.21</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>22.66</v>
+        <v>22.62</v>
       </c>
       <c r="AN16" t="n">
-        <v>22.49</v>
+        <v>22.52</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-1514.83</t>
+          <t>-293.82</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-102.51</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>17846581.03352354</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>4365323.8</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>8308950.7</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>10035732.7</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-3943626</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-418114.0177199567</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-1115833.652546198</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-100.67</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>17865248.04857143</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>5760921</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>8669348.8</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>10064786.9</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-2908427</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>-291255.9022970037</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>-858737.5129378084</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>岱宇</t>
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>155.691</t>
+          <t>233.901</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-33.55</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,49 +7469,49 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>22.74</v>
+        <v>22.66</v>
       </c>
       <c r="AN17" t="n">
-        <v>22.48</v>
+        <v>22.49</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-594.38</t>
+          <t>-1514.83</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-98.14</t>
+          <t>-100.67</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17865248.04857143</t>
+          <t>17846581.03352354</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>7748634.8</v>
+        <v>5760921</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9086934.6</t>
+          <t>8669348.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>9986424.779999999</v>
+        <v>10064786.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1338299</t>
+          <t>-2908427</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-188077.4276350392</t>
+          <t>-291255.9022970037</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-740046.7594637573</t>
+          <t>-858737.5129378084</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>379.722</t>
+          <t>155.691</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,34 +7914,34 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>22.86</v>
+        <v>22.74</v>
       </c>
       <c r="AN18" t="n">
-        <v>22.49</v>
+        <v>22.48</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-169.84</t>
+          <t>-594.38</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-98.14</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17865248.04857143</t>
+          <t>17846581.03352354</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>9180056.199999999</v>
+        <v>7748634.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9536746.8</t>
+          <t>9086934.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>9944544.640000001</v>
+        <v>9986424.779999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-356690</t>
+          <t>-1338299</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-87719.36730254497</t>
+          <t>-188077.4276350392</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-360398.7273771223</t>
+          <t>-740046.7594637573</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>130.298</t>
+          <t>379.722</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,36 +8339,36 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>22.96</v>
+        <v>22.86</v>
       </c>
       <c r="AN19" t="n">
         <v>22.49</v>
@@ -8380,17 +8380,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-75.17</t>
+          <t>-169.84</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-93.42</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>17865248.04857143</t>
+          <t>17846581.03352354</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>10148918</v>
+        <v>9180056.199999999</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>9267970.7</t>
+          <t>9536746.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>9823853.939999999</v>
+        <v>9944544.640000001</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>880947</t>
+          <t>-356690</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-38141.30183444001</t>
+          <t>-87719.36730254497</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-328714.0484184604</t>
+          <t>-360398.7273771223</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>412.554</t>
+          <t>130.298</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,72 +8638,72 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,161 +8769,161 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>22.96</t>
+        </is>
+      </c>
+      <c r="AM20" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-75.17</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-93.42</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>17846581.03352354</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>2895510.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>10148918</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>9267970.7</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>9823853.939999999</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>880947</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-38141.30183444001</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>-328714.0484184604</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2895510.0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>-2.23</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
-      </c>
-      <c r="AM20" t="n">
-        <v>23.08</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>22.48</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-16.29</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-92.18</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>17865248.04857143</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>9391435.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="n">
-        <v>12252577.6</v>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>9667795.1</t>
-        </is>
-      </c>
-      <c r="AZ20" t="n">
-        <v>9822957.84</v>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>2584782</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>14690.10663538189</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>295780.2803945709</t>
-        </is>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>9391435.0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="BN20" t="inlineStr">
         <is>
           <t>11.95148944019183</t>
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>639.921</t>
+          <t>412.554</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,22 +9163,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -9189,49 +9189,49 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>23.13</v>
+        <v>23.08</v>
       </c>
       <c r="AN21" t="n">
-        <v>22.46</v>
+        <v>22.48</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,12 +9240,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-92.18</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17865248.04857143</t>
+          <t>17846581.03352354</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>11577776.6</v>
+        <v>12252577.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9216007.8</t>
+          <t>9667795.1</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>9691364.4</v>
+        <v>9822957.84</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2361768</t>
+          <t>2584782</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-36417.19768447067</t>
+          <t>14690.10663538189</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>481359.4901133813</t>
+          <t>295780.2803945709</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>446.427</t>
+          <t>639.921</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>23.09</v>
+        <v>23.13</v>
       </c>
       <c r="AN22" t="n">
-        <v>22.4</v>
+        <v>22.46</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>31.31</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-92.50</t>
+          <t>-91.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17865248.04857143</t>
+          <t>17846581.03352354</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>10462814.0</t>
+          <t>14958432.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>10425234.4</v>
+        <v>11577776.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>9338847.5</t>
+          <t>9216007.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>9424082.380000001</v>
+        <v>9691364.4</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1086386</t>
+          <t>2361768</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-130558.4136477165</t>
+          <t>-36417.19768447067</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>132817.2722076345</t>
+          <t>481359.4901133813</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>10462814.0</t>
+          <t>14958432.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>561.564</t>
+          <t>446.427</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,74 +9928,74 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-4.9</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>11.63</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-5.86</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>23.25</t>
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>23.05</v>
+        <v>23.09</v>
       </c>
       <c r="AN23" t="n">
-        <v>22.35</v>
+        <v>22.4</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-92.99</t>
+          <t>-92.50</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17865248.04857143</t>
+          <t>17846581.03352354</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>9893437.4</v>
+        <v>10425234.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>9338756.6</t>
+          <t>9338847.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>9295806.699999999</v>
+        <v>9424082.380000001</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>554680</t>
+          <t>1086386</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-178444.901985053</t>
+          <t>-130558.4136477165</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>111829.7011920083</t>
+          <t>132817.2722076345</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>13036399.0</t>
+          <t>10462814.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>801.259</t>
+          <t>315.343</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>57.44</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>80.74</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>162.6</t>
+          <t>162.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>154.43</v>
+        <v>154.68</v>
       </c>
       <c r="AN2" t="n">
-        <v>160.4</v>
+        <v>160.77</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.79</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>184.19</t>
+          <t>319.25</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.99</t>
+          <t>-106.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>129373440.0</t>
+          <t>51178355.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>194736181.4</v>
+        <v>135912887.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>123690210.1</t>
+          <t>125008866.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>158323451.62</v>
+        <v>156640614.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>71045971</t>
+          <t>10904021</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2141214.870208863</t>
+          <t>2309011.167189321</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>11190820.65665781</t>
+          <t>3231890.800581843</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>129373440.0</t>
+          <t>51178355.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>163.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>159.5</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>644.622</t>
+          <t>801.259</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>51.95</t>
+          <t>57.44</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>160.1</t>
+          <t>162.6</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>154.32</v>
+        <v>154.43</v>
       </c>
       <c r="AN3" t="n">
-        <v>159.94</v>
+        <v>160.4</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>155.79</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>130.50</t>
+          <t>184.19</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-116.04</t>
+          <t>-110.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>105803270.0</t>
+          <t>129373440.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>180110241.4</v>
+        <v>194736181.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>118535817.0</t>
+          <t>123690210.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>157797617.5</v>
+        <v>158323451.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>61574424</t>
+          <t>71045971</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>495831.9999454175</t>
+          <t>2141214.870208863</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>13783003.46331429</t>
+          <t>11190820.65665781</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>105803270.0</t>
+          <t>129373440.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1550.62</t>
+          <t>644.622</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>51.95</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>157.1</t>
+          <t>160.1</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>153.9</v>
+        <v>154.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>159.48</v>
+        <v>159.94</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>155.59</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.50</t>
+          <t>130.50</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.28</t>
+          <t>-116.04</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>254889156.0</t>
+          <t>105803270.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>167501275</v>
+        <v>180110241.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>117472813.7</t>
+          <t>118535817.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>157162554.38</v>
+        <v>157797617.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>50028461</t>
+          <t>61574424</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1920017.357030742</t>
+          <t>495831.9999454175</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>19519246.99199092</t>
+          <t>13783003.46331429</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>254889156.0</t>
+          <t>105803270.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>159.5</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>865.777</t>
+          <t>1550.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>152.6</t>
+          <t>157.1</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>153.07</v>
+        <v>153.9</v>
       </c>
       <c r="AN5" t="n">
-        <v>158.92</v>
+        <v>159.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>155.41</t>
+          <t>155.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>91.50</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-126.15</t>
+          <t>-121.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>126447355.6</v>
+        <v>167501275</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>101995133.3</t>
+          <t>117472813.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>153639291.3</v>
+        <v>157162554.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>24452222</t>
+          <t>50028461</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5818065.420489227</t>
+          <t>-1920017.357030742</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>11043276.8546721</t>
+          <t>19519246.99199092</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>161.5</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2163.744</t>
+          <t>865.777</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>149.9</t>
+          <t>152.6</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>152.65</v>
+        <v>153.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>158.59</v>
+        <v>158.92</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>155.37</t>
+          <t>155.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-126.15</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>114104844.4</v>
+        <v>126447355.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>94761718.7</t>
+          <t>101995133.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>152570926.34</v>
+        <v>153639291.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>19343125</t>
+          <t>24452222</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8883764.015973106</t>
+          <t>-5818065.420489227</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>11029874.52083552</t>
+          <t>11043276.8546721</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>161.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>377.931</t>
+          <t>2163.744</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>20.41</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>152.2</v>
+        <v>152.65</v>
       </c>
       <c r="AN7" t="n">
-        <v>158.19</v>
+        <v>158.59</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>155.24</t>
+          <t>155.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.05</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-130.73</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>52644238.8</v>
+        <v>114104844.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>64861349.6</t>
+          <t>94761718.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>147121902.5</v>
+        <v>152570926.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-12217110</t>
+          <t>19343125</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12504425.56812013</t>
+          <t>-8883764.015973106</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-11559046.51038941</t>
+          <t>11029874.52083552</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>289.28</t>
+          <t>377.931</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>-18.84</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>152.38</v>
+        <v>152.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>158.09</v>
+        <v>158.19</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>155.36</t>
+          <t>155.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-23.98</t>
+          <t>-13.05</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-130.73</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>56961392.6</v>
+        <v>52644238.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>65462845.3</t>
+          <t>64861349.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>147489165.54</v>
+        <v>147121902.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-8501452</t>
+          <t>-12217110</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12676312.66952571</t>
+          <t>-12504425.56812013</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-12446351.60819685</t>
+          <t>-11559046.51038941</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>342.425</t>
+          <t>289.28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-12.99</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>152.62</v>
+        <v>152.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>157.92</v>
+        <v>158.09</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>155.51</t>
+          <t>155.36</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-23.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.95</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>67444352.40000001</v>
+        <v>56961392.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>66640291.1</t>
+          <t>65462845.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>147939586.16</v>
+        <v>147489165.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>804061</t>
+          <t>-8501452</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12718123.77158551</t>
+          <t>-12676312.66952571</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-11824563.97620045</t>
+          <t>-12446351.60819685</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>523.223</t>
+          <t>342.425</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>153.07</v>
+        <v>152.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>157.86</v>
+        <v>157.92</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>155.74</t>
+          <t>155.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-125.58</t>
+          <t>-127.95</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>77542911</v>
+        <v>67444352.40000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>67555966.7</t>
+          <t>66640291.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>148067039.32</v>
+        <v>147939586.16</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9986944</t>
+          <t>804061</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-12880589.18892824</t>
+          <t>-12718123.77158551</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-11249110.18134128</t>
+          <t>-11824563.97620045</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-17.56</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>253.617</t>
+          <t>523.223</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.37</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>153.8</v>
+        <v>153.07</v>
       </c>
       <c r="AN11" t="n">
-        <v>157.78</v>
+        <v>157.86</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>155.74</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-32.26</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-125.58</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>75418593</v>
+        <v>77542911</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>69462697.8</t>
+          <t>67555966.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>147915441.16</v>
+        <v>148067039.32</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5955895</t>
+          <t>9986944</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-13177221.73576224</t>
+          <t>-12880589.18892824</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-12916861.75363742</t>
+          <t>-11249110.18134128</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>517.468</t>
+          <t>253.617</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>154.22</v>
+        <v>153.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>157.66</v>
+        <v>157.78</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>156.07</t>
+          <t>155.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-32.75</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-121.94</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>193039349.0970043</t>
+          <t>192873719.7286325</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>77078460.40000001</v>
+        <v>75418593</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>83740554.0</t>
+          <t>69462697.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>148438894.86</v>
+        <v>147915441.16</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-6662093</t>
+          <t>5955895</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-13224559.91433039</t>
+          <t>-13177221.73576224</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-10700633.40143058</t>
+          <t>-12916861.75363742</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>77829509.0</t>
+          <t>37991796.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>143.091</t>
+          <t>129.974</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-37.22</t>
+          <t>-29.83</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,274 +5744,274 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>65.31</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>22.51</v>
+        <v>22.48</v>
       </c>
       <c r="AN13" t="n">
-        <v>22.61</v>
+        <v>22.63</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
+          <t>22.19</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-50.00</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-106.22</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>17827270.19444444</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>2860248.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>3113354.4</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>4437137.7</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>9930130.74</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-1323783</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-800018.9289499772</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-1199231.224326063</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2860248.0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>43.72%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>19.07</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>3905</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>岱宇-運動休閒-上市</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
           <t>22.2</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-42.77</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-105.44</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>17846581.03352354</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>3186447.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="n">
-        <v>3545277.4</v>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>5646956.1</t>
-        </is>
-      </c>
-      <c r="AZ13" t="n">
-        <v>9899078.18</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-2101678</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-727434.8752452343</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-1194735.196205772</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>3186447.0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
+      <c r="CE13" t="inlineStr">
         <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>53.45</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>43.72%</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>19.07</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>4022</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>岱宇-運動休閒-上市</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>22.45</t>
-        </is>
-      </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>196.646</t>
+          <t>143.091</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-37.22</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>65.31</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>22.53</v>
+        <v>22.51</v>
       </c>
       <c r="AN14" t="n">
-        <v>22.58</v>
+        <v>22.61</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-42.77</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17846581.03352354</t>
+          <t>17827270.19444444</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4327422.0</t>
+          <t>3186447.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3569129.4</v>
+        <v>3545277.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>6374592.8</t>
+          <t>5646956.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>10085156.06</v>
+        <v>9899078.18</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2805463</t>
+          <t>-2101678</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-642471.1805251366</t>
+          <t>-727434.8752452343</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1180593.077598007</t>
+          <t>-1194735.196205772</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>4327422.0</t>
+          <t>3186447.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>125.305</t>
+          <t>196.646</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-40.07</t>
+          <t>-44.01</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,63 +6604,63 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>22.56</v>
+        <v>22.53</v>
       </c>
       <c r="AN15" t="n">
-        <v>22.55</v>
+        <v>22.58</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-137.55</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-103.83</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17846581.03352354</t>
+          <t>17827270.19444444</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2779206.0</t>
+          <t>4327422.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>4342063</v>
+        <v>3569129.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7245490.5</t>
+          <t>6374592.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>10018881.82</v>
+        <v>10085156.06</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2903427</t>
+          <t>-2805463</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-544630.8356027965</t>
+          <t>-642471.1805251366</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1240473.333958415</t>
+          <t>-1180593.077598007</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2779206.0</t>
+          <t>4327422.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,42 +6771,42 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>109.472</t>
+          <t>125.305</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-47.46</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,58 +7049,58 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>22.62</v>
+        <v>22.56</v>
       </c>
       <c r="AN16" t="n">
-        <v>22.52</v>
+        <v>22.55</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-293.82</t>
+          <t>-137.55</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-102.51</t>
+          <t>-103.83</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17846581.03352354</t>
+          <t>17827270.19444444</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>4365323.8</v>
+        <v>4342063</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>8308950.7</t>
+          <t>7245490.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>10035732.7</v>
+        <v>10018881.82</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-3943626</t>
+          <t>-2903427</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-418114.0177199567</t>
+          <t>-544630.8356027965</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1115833.652546198</t>
+          <t>-1240473.333958415</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7201,42 +7201,42 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>233.901</t>
+          <t>109.472</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-33.55</t>
+          <t>-47.46</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,151 +7464,151 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>27.21</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>22.66</v>
+        <v>22.62</v>
       </c>
       <c r="AN17" t="n">
-        <v>22.49</v>
+        <v>22.52</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-1514.83</t>
+          <t>-293.82</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-102.51</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>17827270.19444444</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>4365323.8</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>8308950.7</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>10035732.7</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-3943626</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-418114.0177199567</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>-1115833.652546198</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-100.67</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>17846581.03352354</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="n">
-        <v>5760921</v>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>8669348.8</t>
-        </is>
-      </c>
-      <c r="AZ17" t="n">
-        <v>10064786.9</v>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>-2908427</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>-291255.9022970037</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>-858737.5129378084</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>岱宇</t>
@@ -7631,42 +7631,42 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>155.691</t>
+          <t>233.901</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-33.55</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,54 +7894,54 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>22.74</v>
+        <v>22.66</v>
       </c>
       <c r="AN18" t="n">
-        <v>22.48</v>
+        <v>22.49</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-594.38</t>
+          <t>-1514.83</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-98.14</t>
+          <t>-100.67</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17846581.03352354</t>
+          <t>17827270.19444444</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>7748634.8</v>
+        <v>5760921</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9086934.6</t>
+          <t>8669348.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>9986424.779999999</v>
+        <v>10064786.9</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1338299</t>
+          <t>-2908427</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-188077.4276350392</t>
+          <t>-291255.9022970037</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-740046.7594637573</t>
+          <t>-858737.5129378084</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>379.722</t>
+          <t>155.691</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,34 +8344,34 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>22.86</v>
+        <v>22.74</v>
       </c>
       <c r="AN19" t="n">
-        <v>22.49</v>
+        <v>22.48</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8380,17 +8380,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-169.84</t>
+          <t>-594.38</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-98.14</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>17846581.03352354</t>
+          <t>17827270.19444444</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>9180056.199999999</v>
+        <v>7748634.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>9536746.8</t>
+          <t>9086934.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>9944544.640000001</v>
+        <v>9986424.779999999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-356690</t>
+          <t>-1338299</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-87719.36730254497</t>
+          <t>-188077.4276350392</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-360398.7273771223</t>
+          <t>-740046.7594637573</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>130.298</t>
+          <t>379.722</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,36 +8769,36 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>22.96</v>
+        <v>22.86</v>
       </c>
       <c r="AN20" t="n">
         <v>22.49</v>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-75.17</t>
+          <t>-169.84</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-93.42</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17846581.03352354</t>
+          <t>17827270.19444444</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>10148918</v>
+        <v>9180056.199999999</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>9267970.7</t>
+          <t>9536746.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>9823853.939999999</v>
+        <v>9944544.640000001</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>880947</t>
+          <t>-356690</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-38141.30183444001</t>
+          <t>-87719.36730254497</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-328714.0484184604</t>
+          <t>-360398.7273771223</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>412.554</t>
+          <t>130.298</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,72 +9068,72 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,60 +9199,60 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>23.08</v>
+        <v>22.96</v>
       </c>
       <c r="AN21" t="n">
-        <v>22.48</v>
+        <v>22.49</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-75.17</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-92.18</t>
+          <t>-93.42</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9270,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17846581.03352354</t>
+          <t>17827270.19444444</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>9391435.0</t>
+          <t>2895510.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>12252577.6</v>
+        <v>10148918</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9667795.1</t>
+          <t>9267970.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>9822957.84</v>
+        <v>9823853.939999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2584782</t>
+          <t>880947</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>14690.10663538189</t>
+          <t>-38141.30183444001</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>295780.2803945709</t>
+          <t>-328714.0484184604</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>9391435.0</t>
+          <t>2895510.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>639.921</t>
+          <t>412.554</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,75 +9593,75 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>23.13</v>
+        <v>23.08</v>
       </c>
       <c r="AN22" t="n">
-        <v>22.46</v>
+        <v>22.48</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-92.18</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17846581.03352354</t>
+          <t>17827270.19444444</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>11577776.6</v>
+        <v>12252577.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>9216007.8</t>
+          <t>9667795.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>9691364.4</v>
+        <v>9822957.84</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2361768</t>
+          <t>2584782</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-36417.19768447067</t>
+          <t>14690.10663538189</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>481359.4901133813</t>
+          <t>295780.2803945709</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,42 +9781,42 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>446.427</t>
+          <t>639.921</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>23.09</v>
+        <v>23.13</v>
       </c>
       <c r="AN23" t="n">
-        <v>22.4</v>
+        <v>22.46</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>31.31</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-92.50</t>
+          <t>-91.86</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17846581.03352354</t>
+          <t>17827270.19444444</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>10462814.0</t>
+          <t>14958432.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>10425234.4</v>
+        <v>11577776.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>9338847.5</t>
+          <t>9216007.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>9424082.380000001</v>
+        <v>9691364.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1086386</t>
+          <t>2361768</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-130558.4136477165</t>
+          <t>-36417.19768447067</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>132817.2722076345</t>
+          <t>481359.4901133813</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>10462814.0</t>
+          <t>14958432.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>315.343</t>
+          <t>267.22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>80.74</t>
+          <t>77.89</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>162.8</t>
+          <t>163.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>154.68</v>
+        <v>155.05</v>
       </c>
       <c r="AN2" t="n">
-        <v>160.77</v>
+        <v>160.94</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>155.81</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>319.25</t>
+          <t>990.61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.11</t>
+          <t>-101.76</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>51178355.0</t>
+          <t>43290801.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>135912887.6</v>
+        <v>116907004.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>125008866.0</t>
+          <t>121677180.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>156640614.54</v>
+        <v>150652659.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>10904021</t>
+          <t>-4770175</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2309011.167189321</t>
+          <t>1490436.538593134</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>3231890.800581843</t>
+          <t>-3011723.918685898</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>51178355.0</t>
+          <t>43290801.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>163.5</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>163.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>162.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>163.5</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>163.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>801.259</t>
+          <t>315.343</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>57.44</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>80.74</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>162.6</t>
+          <t>162.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>154.43</v>
+        <v>154.68</v>
       </c>
       <c r="AN3" t="n">
-        <v>160.4</v>
+        <v>160.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>155.79</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>184.19</t>
+          <t>319.25</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.99</t>
+          <t>-106.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>129373440.0</t>
+          <t>51178355.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>194736181.4</v>
+        <v>135912887.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>123690210.1</t>
+          <t>125008866.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>158323451.62</v>
+        <v>156640614.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>71045971</t>
+          <t>10904021</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2141214.870208863</t>
+          <t>2309011.167189321</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>11190820.65665781</t>
+          <t>3231890.800581843</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>129373440.0</t>
+          <t>51178355.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>163.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>159.5</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>644.622</t>
+          <t>801.259</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>51.95</t>
+          <t>57.44</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>160.1</t>
+          <t>162.6</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>154.32</v>
+        <v>154.43</v>
       </c>
       <c r="AN4" t="n">
-        <v>159.94</v>
+        <v>160.4</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>155.79</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>130.50</t>
+          <t>184.19</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-116.04</t>
+          <t>-110.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>105803270.0</t>
+          <t>129373440.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>180110241.4</v>
+        <v>194736181.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>118535817.0</t>
+          <t>123690210.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>157797617.5</v>
+        <v>158323451.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>61574424</t>
+          <t>71045971</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>495831.9999454175</t>
+          <t>2141214.870208863</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>13783003.46331429</t>
+          <t>11190820.65665781</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>105803270.0</t>
+          <t>129373440.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1550.62</t>
+          <t>644.622</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>51.95</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>157.1</t>
+          <t>160.1</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>153.9</v>
+        <v>154.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>159.48</v>
+        <v>159.94</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>155.59</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.50</t>
+          <t>130.50</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.28</t>
+          <t>-116.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>254889156.0</t>
+          <t>105803270.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>167501275</v>
+        <v>180110241.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>117472813.7</t>
+          <t>118535817.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>157162554.38</v>
+        <v>157797617.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>50028461</t>
+          <t>61574424</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1920017.357030742</t>
+          <t>495831.9999454175</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>19519246.99199092</t>
+          <t>13783003.46331429</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>254889156.0</t>
+          <t>105803270.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>159.5</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>865.777</t>
+          <t>1550.62</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>152.6</t>
+          <t>157.1</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>153.07</v>
+        <v>153.9</v>
       </c>
       <c r="AN6" t="n">
-        <v>158.92</v>
+        <v>159.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>155.41</t>
+          <t>155.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>91.50</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-126.15</t>
+          <t>-121.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>126447355.6</v>
+        <v>167501275</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>101995133.3</t>
+          <t>117472813.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>153639291.3</v>
+        <v>157162554.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>24452222</t>
+          <t>50028461</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5818065.420489227</t>
+          <t>-1920017.357030742</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>11043276.8546721</t>
+          <t>19519246.99199092</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>161.5</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2163.744</t>
+          <t>865.777</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>149.9</t>
+          <t>152.6</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>152.65</v>
+        <v>153.07</v>
       </c>
       <c r="AN7" t="n">
-        <v>158.59</v>
+        <v>158.92</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>155.37</t>
+          <t>155.41</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-126.15</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>114104844.4</v>
+        <v>126447355.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>94761718.7</t>
+          <t>101995133.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>152570926.34</v>
+        <v>153639291.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>19343125</t>
+          <t>24452222</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8883764.015973106</t>
+          <t>-5818065.420489227</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>11029874.52083552</t>
+          <t>11043276.8546721</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>161.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>377.931</t>
+          <t>2163.744</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>20.41</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>152.2</v>
+        <v>152.65</v>
       </c>
       <c r="AN8" t="n">
-        <v>158.19</v>
+        <v>158.59</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>155.24</t>
+          <t>155.37</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.05</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-130.73</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>52644238.8</v>
+        <v>114104844.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>64861349.6</t>
+          <t>94761718.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>147121902.5</v>
+        <v>152570926.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-12217110</t>
+          <t>19343125</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12504425.56812013</t>
+          <t>-8883764.015973106</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-11559046.51038941</t>
+          <t>11029874.52083552</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>289.28</t>
+          <t>377.931</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>-18.84</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>152.38</v>
+        <v>152.2</v>
       </c>
       <c r="AN9" t="n">
-        <v>158.09</v>
+        <v>158.19</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>155.36</t>
+          <t>155.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-23.98</t>
+          <t>-13.05</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-130.73</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>56961392.6</v>
+        <v>52644238.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>65462845.3</t>
+          <t>64861349.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>147489165.54</v>
+        <v>147121902.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-8501452</t>
+          <t>-12217110</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12676312.66952571</t>
+          <t>-12504425.56812013</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-12446351.60819685</t>
+          <t>-11559046.51038941</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>342.425</t>
+          <t>289.28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-12.99</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>152.62</v>
+        <v>152.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>157.92</v>
+        <v>158.09</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>155.51</t>
+          <t>155.36</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-23.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-127.95</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>67444352.40000001</v>
+        <v>56961392.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>66640291.1</t>
+          <t>65462845.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>147939586.16</v>
+        <v>147489165.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>804061</t>
+          <t>-8501452</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-12718123.77158551</t>
+          <t>-12676312.66952571</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-11824563.97620045</t>
+          <t>-12446351.60819685</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>523.223</t>
+          <t>342.425</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>153.07</v>
+        <v>152.62</v>
       </c>
       <c r="AN11" t="n">
-        <v>157.86</v>
+        <v>157.92</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>155.74</t>
+          <t>155.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-125.58</t>
+          <t>-127.95</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>77542911</v>
+        <v>67444352.40000001</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>67555966.7</t>
+          <t>66640291.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>148067039.32</v>
+        <v>147939586.16</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9986944</t>
+          <t>804061</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-12880589.18892824</t>
+          <t>-12718123.77158551</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-11249110.18134128</t>
+          <t>-11824563.97620045</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.56</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>253.617</t>
+          <t>523.223</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.37</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>153.8</v>
+        <v>153.07</v>
       </c>
       <c r="AN12" t="n">
-        <v>157.78</v>
+        <v>157.86</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>155.74</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-32.26</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-125.58</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>192873719.7286325</t>
+          <t>192691731.7937411</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>75418593</v>
+        <v>77542911</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>69462697.8</t>
+          <t>67555966.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>147915441.16</v>
+        <v>148067039.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5955895</t>
+          <t>9986944</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-13177221.73576224</t>
+          <t>-12880589.18892824</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-12916861.75363742</t>
+          <t>-11249110.18134128</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>37991796.0</t>
+          <t>76607661.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-17.56</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>49453</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>129.974</t>
+          <t>232.902</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-29.83</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,54 +5744,54 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>22.48</v>
+        <v>22.44</v>
       </c>
       <c r="AN13" t="n">
-        <v>22.63</v>
+        <v>22.64</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5800,17 +5800,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-43.83</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-106.22</t>
+          <t>-106.98</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17827270.19444444</t>
+          <t>17812675.01351351</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2860248.0</t>
+          <t>5044572.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3113354.4</v>
+        <v>3639579</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4437137.7</t>
+          <t>4002451.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>9930130.74</v>
+        <v>9969580.199999999</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1323783</t>
+          <t>-362872</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-800018.9289499772</t>
+          <t>-832104.2265579985</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1199231.224326063</t>
+          <t>-1008573.363402115</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2860248.0</t>
+          <t>5044572.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>143.091</t>
+          <t>129.974</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-37.22</t>
+          <t>-29.83</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,274 +6174,274 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>65.31</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>22.51</v>
+        <v>22.48</v>
       </c>
       <c r="AN14" t="n">
-        <v>22.61</v>
+        <v>22.63</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
+          <t>22.19</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-50.00</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-106.22</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>17812675.01351351</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>2860248.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>3113354.4</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>4437137.7</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>9930130.74</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-1323783</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-800018.9289499772</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-1199231.224326063</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2860248.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>52.14</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>43.72%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>3923</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>岱宇-運動休閒-上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
           <t>22.2</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-42.77</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-105.44</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>17827270.19444444</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>3186447.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="n">
-        <v>3545277.4</v>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>5646956.1</t>
-        </is>
-      </c>
-      <c r="AZ14" t="n">
-        <v>9899078.18</v>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-2101678</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-727434.8752452343</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-1194735.196205772</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>3186447.0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
+      <c r="CE14" t="inlineStr">
         <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>43.72%</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>19.07</t>
-        </is>
-      </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>3905</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>岱宇-運動休閒-上市</t>
-        </is>
-      </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>22.45</t>
-        </is>
-      </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>196.646</t>
+          <t>143.091</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-37.22</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>65.31</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>22.53</v>
+        <v>22.51</v>
       </c>
       <c r="AN15" t="n">
-        <v>22.58</v>
+        <v>22.61</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-42.77</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17827270.19444444</t>
+          <t>17812675.01351351</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4327422.0</t>
+          <t>3186447.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3569129.4</v>
+        <v>3545277.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6374592.8</t>
+          <t>5646956.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>10085156.06</v>
+        <v>9899078.18</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2805463</t>
+          <t>-2101678</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-642471.1805251366</t>
+          <t>-727434.8752452343</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1180593.077598007</t>
+          <t>-1194735.196205772</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>4327422.0</t>
+          <t>3186447.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>125.305</t>
+          <t>196.646</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-40.07</t>
+          <t>-44.01</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,63 +7034,63 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>22.56</v>
+        <v>22.53</v>
       </c>
       <c r="AN16" t="n">
-        <v>22.55</v>
+        <v>22.58</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-137.55</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-103.83</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17827270.19444444</t>
+          <t>17812675.01351351</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2779206.0</t>
+          <t>4327422.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>4342063</v>
+        <v>3569129.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7245490.5</t>
+          <t>6374592.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>10018881.82</v>
+        <v>10085156.06</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2903427</t>
+          <t>-2805463</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-544630.8356027965</t>
+          <t>-642471.1805251366</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1240473.333958415</t>
+          <t>-1180593.077598007</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2779206.0</t>
+          <t>4327422.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>109.472</t>
+          <t>125.305</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-47.46</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7479,58 +7479,58 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>22.62</v>
+        <v>22.56</v>
       </c>
       <c r="AN17" t="n">
-        <v>22.52</v>
+        <v>22.55</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-293.82</t>
+          <t>-137.55</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-102.51</t>
+          <t>-103.83</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17827270.19444444</t>
+          <t>17812675.01351351</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>4365323.8</v>
+        <v>4342063</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>8308950.7</t>
+          <t>7245490.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>10035732.7</v>
+        <v>10018881.82</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3943626</t>
+          <t>-2903427</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-418114.0177199567</t>
+          <t>-544630.8356027965</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1115833.652546198</t>
+          <t>-1240473.333958415</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>233.901</t>
+          <t>109.472</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.55</t>
+          <t>-47.46</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,151 +7894,151 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>27.21</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>22.66</v>
+        <v>22.62</v>
       </c>
       <c r="AN18" t="n">
-        <v>22.49</v>
+        <v>22.52</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-1514.83</t>
+          <t>-293.82</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-102.51</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>17812675.01351351</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>4365323.8</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>8308950.7</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>10035732.7</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-3943626</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-418114.0177199567</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>-1115833.652546198</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-100.67</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>17827270.19444444</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="n">
-        <v>5760921</v>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>8669348.8</t>
-        </is>
-      </c>
-      <c r="AZ18" t="n">
-        <v>10064786.9</v>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>-2908427</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>-291255.9022970037</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>-858737.5129378084</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>岱宇</t>
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>155.691</t>
+          <t>233.901</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-33.55</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,54 +8324,54 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>22.74</v>
+        <v>22.66</v>
       </c>
       <c r="AN19" t="n">
-        <v>22.48</v>
+        <v>22.49</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8380,17 +8380,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-594.38</t>
+          <t>-1514.83</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-98.14</t>
+          <t>-100.67</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>17827270.19444444</t>
+          <t>17812675.01351351</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>7748634.8</v>
+        <v>5760921</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>9086934.6</t>
+          <t>8669348.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>9986424.779999999</v>
+        <v>10064786.9</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1338299</t>
+          <t>-2908427</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-188077.4276350392</t>
+          <t>-291255.9022970037</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-740046.7594637573</t>
+          <t>-858737.5129378084</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>379.722</t>
+          <t>155.691</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,34 +8774,34 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>22.86</v>
+        <v>22.74</v>
       </c>
       <c r="AN20" t="n">
-        <v>22.49</v>
+        <v>22.48</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-169.84</t>
+          <t>-594.38</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-98.14</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17827270.19444444</t>
+          <t>17812675.01351351</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>9180056.199999999</v>
+        <v>7748634.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>9536746.8</t>
+          <t>9086934.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>9944544.640000001</v>
+        <v>9986424.779999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-356690</t>
+          <t>-1338299</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-87719.36730254497</t>
+          <t>-188077.4276350392</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-360398.7273771223</t>
+          <t>-740046.7594637573</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>130.298</t>
+          <t>379.722</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,36 +9199,36 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>22.96</v>
+        <v>22.86</v>
       </c>
       <c r="AN21" t="n">
         <v>22.49</v>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-75.17</t>
+          <t>-169.84</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-93.42</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17827270.19444444</t>
+          <t>17812675.01351351</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>10148918</v>
+        <v>9180056.199999999</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9267970.7</t>
+          <t>9536746.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>9823853.939999999</v>
+        <v>9944544.640000001</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>880947</t>
+          <t>-356690</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-38141.30183444001</t>
+          <t>-87719.36730254497</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-328714.0484184604</t>
+          <t>-360398.7273771223</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2895510.0</t>
+          <t>8192090.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>412.554</t>
+          <t>130.298</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,72 +9498,72 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-2.43</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-2.29</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>26.74</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,60 +9629,60 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>23.08</v>
+        <v>22.96</v>
       </c>
       <c r="AN22" t="n">
-        <v>22.48</v>
+        <v>22.49</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-75.17</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-92.18</t>
+          <t>-93.42</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17827270.19444444</t>
+          <t>17812675.01351351</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9391435.0</t>
+          <t>2895510.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>12252577.6</v>
+        <v>10148918</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>9667795.1</t>
+          <t>9267970.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>9822957.84</v>
+        <v>9823853.939999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2584782</t>
+          <t>880947</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>14690.10663538189</t>
+          <t>-38141.30183444001</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>295780.2803945709</t>
+          <t>-328714.0484184604</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>9391435.0</t>
+          <t>2895510.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>639.921</t>
+          <t>412.554</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,75 +10023,75 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>23.13</v>
+        <v>23.08</v>
       </c>
       <c r="AN23" t="n">
-        <v>22.46</v>
+        <v>22.48</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10100,12 +10100,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-91.86</t>
+          <t>-92.18</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17827270.19444444</t>
+          <t>17812675.01351351</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>11577776.6</v>
+        <v>12252577.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>9216007.8</t>
+          <t>9667795.1</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>9691364.4</v>
+        <v>9822957.84</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2361768</t>
+          <t>2584782</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-36417.19768447067</t>
+          <t>14690.10663538189</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>481359.4901133813</t>
+          <t>295780.2803945709</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>14958432.0</t>
+          <t>9391435.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/健身器材.xlsx
+++ b/Result/checksun_type/健身器材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>267.22</t>
+          <t>684.019</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-31.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>77.89</t>
+          <t>66.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>163.4</t>
+          <t>161.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>155.05</v>
+        <v>155.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>160.94</v>
+        <v>160.98</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>155.81</t>
+          <t>155.76</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>990.61</t>
+          <t>984.69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.76</t>
+          <t>-98.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>43290801.0</t>
+          <t>108567492.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>116907004.4</v>
+        <v>87642671.59999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>121677180.0</t>
+          <t>127571973.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>150652659.78</v>
+        <v>148205810.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4770175</t>
+          <t>-39929301</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1490436.538593134</t>
+          <t>890183.3327778566</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3011723.918685898</t>
+          <t>-2411209.299206167</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>43290801.0</t>
+          <t>108567492.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-11.05</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>163.5</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>163.5</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>315.343</t>
+          <t>267.22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>80.74</t>
+          <t>77.89</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>162.8</t>
+          <t>163.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>154.68</v>
+        <v>155.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>160.77</v>
+        <v>160.94</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>155.81</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>319.25</t>
+          <t>990.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.11</t>
+          <t>-101.76</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>51178355.0</t>
+          <t>43290801.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>135912887.6</v>
+        <v>116907004.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>125008866.0</t>
+          <t>121677180.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>156640614.54</v>
+        <v>150652659.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>10904021</t>
+          <t>-4770175</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2309011.167189321</t>
+          <t>1490436.538593134</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>3231890.800581843</t>
+          <t>-3011723.918685898</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>51178355.0</t>
+          <t>43290801.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>163.5</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>163.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>162.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>163.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>163.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>801.259</t>
+          <t>315.343</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>57.44</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>80.74</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>162.6</t>
+          <t>162.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>154.43</v>
+        <v>154.68</v>
       </c>
       <c r="AN4" t="n">
-        <v>160.4</v>
+        <v>160.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>155.79</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>184.19</t>
+          <t>319.25</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.99</t>
+          <t>-106.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>129373440.0</t>
+          <t>51178355.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>194736181.4</v>
+        <v>135912887.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>123690210.1</t>
+          <t>125008866.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>158323451.62</v>
+        <v>156640614.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>71045971</t>
+          <t>10904021</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2141214.870208863</t>
+          <t>2309011.167189321</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>11190820.65665781</t>
+          <t>3231890.800581843</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>129373440.0</t>
+          <t>51178355.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>163.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>159.5</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>644.622</t>
+          <t>801.259</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.95</t>
+          <t>57.44</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>160.1</t>
+          <t>162.6</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>154.32</v>
+        <v>154.43</v>
       </c>
       <c r="AN5" t="n">
-        <v>159.94</v>
+        <v>160.4</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>155.72</t>
+          <t>155.79</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>130.50</t>
+          <t>184.19</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-116.04</t>
+          <t>-110.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>105803270.0</t>
+          <t>129373440.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>180110241.4</v>
+        <v>194736181.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>118535817.0</t>
+          <t>123690210.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>157797617.5</v>
+        <v>158323451.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>61574424</t>
+          <t>71045971</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>495831.9999454175</t>
+          <t>2141214.870208863</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>13783003.46331429</t>
+          <t>11190820.65665781</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>105803270.0</t>
+          <t>129373440.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1550.62</t>
+          <t>644.622</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>51.95</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>157.1</t>
+          <t>160.1</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>153.9</v>
+        <v>154.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>159.48</v>
+        <v>159.94</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>155.59</t>
+          <t>155.72</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.50</t>
+          <t>130.50</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.28</t>
+          <t>-116.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>254889156.0</t>
+          <t>105803270.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>167501275</v>
+        <v>180110241.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>117472813.7</t>
+          <t>118535817.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>157162554.38</v>
+        <v>157797617.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>50028461</t>
+          <t>61574424</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1920017.357030742</t>
+          <t>495831.9999454175</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>19519246.99199092</t>
+          <t>13783003.46331429</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>254889156.0</t>
+          <t>105803270.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>168.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>159.5</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>865.777</t>
+          <t>1550.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>152.6</t>
+          <t>157.1</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>153.07</v>
+        <v>153.9</v>
       </c>
       <c r="AN7" t="n">
-        <v>158.92</v>
+        <v>159.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>155.41</t>
+          <t>155.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>91.50</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.15</t>
+          <t>-121.28</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>126447355.6</v>
+        <v>167501275</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>101995133.3</t>
+          <t>117472813.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>153639291.3</v>
+        <v>157162554.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>24452222</t>
+          <t>50028461</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5818065.420489227</t>
+          <t>-1920017.357030742</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>11043276.8546721</t>
+          <t>19519246.99199092</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>138320217.0</t>
+          <t>254889156.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>161.5</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2163.744</t>
+          <t>865.777</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>149.9</t>
+          <t>152.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>152.65</v>
+        <v>153.07</v>
       </c>
       <c r="AN8" t="n">
-        <v>158.59</v>
+        <v>158.92</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>155.37</t>
+          <t>155.41</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-126.15</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>114104844.4</v>
+        <v>126447355.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>94761718.7</t>
+          <t>101995133.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>152570926.34</v>
+        <v>153639291.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>19343125</t>
+          <t>24452222</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8883764.015973106</t>
+          <t>-5818065.420489227</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>11029874.52083552</t>
+          <t>11043276.8546721</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>345294824.0</t>
+          <t>138320217.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>161.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>377.931</t>
+          <t>2163.744</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.84</t>
+          <t>20.41</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>152.2</v>
+        <v>152.65</v>
       </c>
       <c r="AN9" t="n">
-        <v>158.19</v>
+        <v>158.59</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>155.24</t>
+          <t>155.37</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.05</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-130.73</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>52644238.8</v>
+        <v>114104844.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>64861349.6</t>
+          <t>94761718.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>147121902.5</v>
+        <v>152570926.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-12217110</t>
+          <t>19343125</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12504425.56812013</t>
+          <t>-8883764.015973106</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-11559046.51038941</t>
+          <t>11029874.52083552</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>56243740.0</t>
+          <t>345294824.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.30</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>289.28</t>
+          <t>377.931</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.99</t>
+          <t>-18.84</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>29.21</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>152.38</v>
+        <v>152.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>158.09</v>
+        <v>158.19</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>155.36</t>
+          <t>155.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-23.98</t>
+          <t>-13.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.73</t>
+          <t>-130.73</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>56961392.6</v>
+        <v>52644238.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>65462845.3</t>
+          <t>64861349.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>147489165.54</v>
+        <v>147121902.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-8501452</t>
+          <t>-12217110</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-12676312.66952571</t>
+          <t>-12504425.56812013</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-12446351.60819685</t>
+          <t>-11559046.51038941</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>42758438.0</t>
+          <t>56243740.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-15.30</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>342.425</t>
+          <t>289.28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-12.99</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>152.62</v>
+        <v>152.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>157.92</v>
+        <v>158.09</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>155.51</t>
+          <t>155.36</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-23.98</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-127.95</t>
+          <t>-129.73</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>67444352.40000001</v>
+        <v>56961392.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>66640291.1</t>
+          <t>65462845.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>147939586.16</v>
+        <v>147489165.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>804061</t>
+          <t>-8501452</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-12718123.77158551</t>
+          <t>-12676312.66952571</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-11824563.97620045</t>
+          <t>-12446351.60819685</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>49619559.0</t>
+          <t>42758438.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>523.223</t>
+          <t>342.425</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>684</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>153.07</v>
+        <v>152.62</v>
       </c>
       <c r="AN12" t="n">
-        <v>157.86</v>
+        <v>157.92</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>155.74</t>
+          <t>155.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-125.58</t>
+          <t>-127.95</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>192691731.7937411</t>
+          <t>192649344.7286932</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>77542911</v>
+        <v>67444352.40000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>67555966.7</t>
+          <t>66640291.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>148067039.32</v>
+        <v>147939586.16</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9986944</t>
+          <t>804061</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-12880589.18892824</t>
+          <t>-12718123.77158551</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-11249110.18134128</t>
+          <t>-11824563.97620045</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>76607661.0</t>
+          <t>49619559.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.56</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>232.902</t>
+          <t>63.474</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,63 +5744,63 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
           <t>59.26</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>70.37</t>
-        </is>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AM13" t="n">
         <v>22.44</v>
       </c>
       <c r="AN13" t="n">
-        <v>22.64</v>
+        <v>22.66</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-43.83</t>
+          <t>-32.71</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-106.98</t>
+          <t>-107.60</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17812675.01351351</t>
+          <t>17790350.11150568</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>5044572.0</t>
+          <t>1397296.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3639579</v>
+        <v>3363197</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4002451.4</t>
+          <t>3852630.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>9969580.199999999</v>
+        <v>9974810.42</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-362872</t>
+          <t>-489433</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-832104.2265579985</t>
+          <t>-876925.7650368139</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1008573.363402115</t>
+          <t>-1123444.226670299</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>5044572.0</t>
+          <t>1397296.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>129.974</t>
+          <t>232.902</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-29.83</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,54 +6174,54 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>22.48</v>
+        <v>22.44</v>
       </c>
       <c r="AN14" t="n">
-        <v>22.63</v>
+        <v>22.64</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6230,17 +6230,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-43.83</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-106.22</t>
+          <t>-106.98</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17812675.01351351</t>
+          <t>17790350.11150568</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2860248.0</t>
+          <t>5044572.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3113354.4</v>
+        <v>3639579</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>4437137.7</t>
+          <t>4002451.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>9930130.74</v>
+        <v>9969580.199999999</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1323783</t>
+          <t>-362872</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-800018.9289499772</t>
+          <t>-832104.2265579985</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1199231.224326063</t>
+          <t>-1008573.363402115</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2860248.0</t>
+          <t>5044572.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>143.091</t>
+          <t>129.974</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-37.22</t>
+          <t>-29.83</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,274 +6604,274 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>65.31</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>22.51</v>
+        <v>22.48</v>
       </c>
       <c r="AN15" t="n">
-        <v>22.61</v>
+        <v>22.63</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
+          <t>22.19</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-50.00</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-106.22</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>17790350.11150568</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>2860248.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>3113354.4</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>4437137.7</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>9930130.74</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-1323783</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-800018.9289499772</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-1199231.224326063</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2860248.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>岱宇</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>11.95148944019183</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>-23.56482151964889</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>-10.04313818682466</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>52.38</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>43.72%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>3941</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>岱宇-運動休閒-上市</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
           <t>22.2</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-42.77</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-105.44</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>17812675.01351351</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>3186447.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>3545277.4</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>5646956.1</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>9899078.18</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-2101678</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-727434.8752452343</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-1194735.196205772</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>3186447.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
+      <c r="CE15" t="inlineStr">
         <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>岱宇</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>11.95148944019183</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>-23.56482151964889</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>-10.04313818682466</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>52.14</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>43.72%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>電動跑步機55.06%、其他17.48%、橢圓機13.13%、健身車10.51%、家具3.82% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>岱宇-運動休閒-上市</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>22.45</t>
-        </is>
-      </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>196.646</t>
+          <t>143.091</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-37.22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>65.31</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>22.53</v>
+        <v>22.51</v>
       </c>
       <c r="AN16" t="n">
-        <v>22.58</v>
+        <v>22.61</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-84.59</t>
+          <t>-42.77</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17812675.01351351</t>
+          <t>17790350.11150568</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4327422.0</t>
+          <t>3186447.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3569129.4</v>
+        <v>3545277.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6374592.8</t>
+          <t>5646956.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>10085156.06</v>
+        <v>9899078.18</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2805463</t>
+          <t>-2101678</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-642471.1805251366</t>
+          <t>-727434.8752452343</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1180593.077598007</t>
+          <t>-1194735.196205772</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>4327422.0</t>
+          <t>3186447.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>125.305</t>
+          <t>196.646</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-40.07</t>
+          <t>-44.01</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,63 +7464,63 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>22.56</v>
+        <v>22.53</v>
       </c>
       <c r="AN17" t="n">
-        <v>22.55</v>
+        <v>22.58</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-137.55</t>
+          <t>-84.59</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-103.83</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17812675.01351351</t>
+          <t>17790350.11150568</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2779206.0</t>
+          <t>4327422.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>4342063</v>
+        <v>3569129.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7245490.5</t>
+          <t>6374592.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>10018881.82</v>
+        <v>10085156.06</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2903427</t>
+          <t>-2805463</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-544630.8356027965</t>
+          <t>-642471.1805251366</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1240473.333958415</t>
+          <t>-1180593.077598007</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2779206.0</t>
+          <t>4327422.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>109.472</t>
+          <t>125.305</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-47.46</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,58 +7909,58 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>22.62</v>
+        <v>22.56</v>
       </c>
       <c r="AN18" t="n">
-        <v>22.52</v>
+        <v>22.55</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-293.82</t>
+          <t>-137.55</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-102.51</t>
+          <t>-103.83</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17812675.01351351</t>
+          <t>17790350.11150568</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>4365323.8</v>
+        <v>4342063</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>8308950.7</t>
+          <t>7245490.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>10035732.7</v>
+        <v>10018881.82</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-3943626</t>
+          <t>-2903427</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-418114.0177199567</t>
+          <t>-544630.8356027965</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1115833.652546198</t>
+          <t>-1240473.333958415</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2413449.0</t>
+          <t>2779206.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>233.901</t>
+          <t>109.472</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.55</t>
+          <t>-47.46</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,151 +8324,151 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>27.21</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>22.66</v>
+        <v>22.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>22.49</v>
+        <v>22.52</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-1514.83</t>
+          <t>-293.82</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-102.51</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>17790350.11150568</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>4365323.8</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>8308950.7</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>10035732.7</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-3943626</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-418114.0177199567</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-1115833.652546198</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2413449.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-100.67</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>17812675.01351351</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>5760921</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>8669348.8</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>10064786.9</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>-2908427</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-291255.9022970037</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>-858737.5129378084</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>5019863.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>岱宇</t>
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>155.691</t>
+          <t>233.901</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-14.73</t>
+          <t>-33.55</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,54 +8754,54 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.76</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>22.74</v>
+        <v>22.66</v>
       </c>
       <c r="AN20" t="n">
-        <v>22.48</v>
+        <v>22.49</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-594.38</t>
+          <t>-1514.83</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-98.14</t>
+          <t>-100.67</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17812675.01351351</t>
+          <t>17790350.11150568</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>7748634.8</v>
+        <v>5760921</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>9086934.6</t>
+          <t>8669348.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>9986424.779999999</v>
+        <v>10064786.9</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1338299</t>
+          <t>-2908427</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-188077.4276350392</t>
+          <t>-291255.9022970037</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-740046.7594637573</t>
+          <t>-858737.5129378084</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>3305707.0</t>
+          <t>5019863.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>379.722</t>
+          <t>155.691</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-14.73</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,34 +9204,34 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>22.86</v>
+        <v>22.74</v>
       </c>
       <c r="AN21" t="n">
-        <v>22.49</v>
+        <v>22.48</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-169.84</t>
+          <t>-594.38</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-98.14</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17812675.01351351</t>
+          <t>17790350.11150568</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>8192090.0</t>
+          <t>3305707.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>9180056.199999999</v>
+        <v>7748634.8</v>
       </c>
       <c r